--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,19 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\4semestre\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFE4A6BF-AC00-40C8-8669-13E3CC710A3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F5EDE8-3892-449B-80F3-2DAE790CD2CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
     <sheet name="alunos" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1950" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="52">
   <si>
     <t>TER</t>
   </si>
@@ -617,36 +616,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="39" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.7109375" customWidth="1"/>
-    <col min="42" max="46" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="39" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.6640625" customWidth="1"/>
+    <col min="42" max="46" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="7" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="7" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="7" style="4" bestFit="1" customWidth="1"/>
     <col min="52" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="59" width="7.7109375" customWidth="1"/>
-    <col min="60" max="60" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="61" max="106" width="7.7109375" customWidth="1"/>
+    <col min="55" max="59" width="7.6640625" customWidth="1"/>
+    <col min="60" max="60" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="61" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -821,8 +820,12 @@
       <c r="BI1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="BJ1" s="1"/>
-      <c r="BK1" s="1"/>
+      <c r="BJ1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="BL1" s="1"/>
       <c r="BM1" s="1"/>
       <c r="BN1" s="3"/>
@@ -852,7 +855,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1037,8 +1040,12 @@
       <c r="BI2" s="1">
         <v>46275</v>
       </c>
-      <c r="BJ2" s="1"/>
-      <c r="BK2" s="1"/>
+      <c r="BJ2" s="1">
+        <v>46280</v>
+      </c>
+      <c r="BK2" s="1">
+        <v>46282</v>
+      </c>
       <c r="BL2" s="1"/>
       <c r="BM2" s="1"/>
       <c r="BN2" s="4"/>
@@ -1068,7 +1075,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1252,7 +1259,9 @@
       <c r="BI3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ3" s="4"/>
+      <c r="BJ3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK3" s="4"/>
       <c r="BL3" s="4"/>
       <c r="BM3" s="4"/>
@@ -1315,7 +1324,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1499,7 +1508,9 @@
       <c r="BI4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ4" s="4"/>
+      <c r="BJ4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK4" s="4"/>
       <c r="BL4" s="4"/>
       <c r="BM4" s="4"/>
@@ -1562,7 +1573,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1746,7 +1757,9 @@
       <c r="BI5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ5" s="4"/>
+      <c r="BJ5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK5" s="4"/>
       <c r="BL5" s="4"/>
       <c r="BM5" s="4"/>
@@ -1809,7 +1822,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -1993,7 +2006,9 @@
       <c r="BI6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BJ6" s="4"/>
+      <c r="BJ6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK6" s="4"/>
       <c r="BL6" s="4"/>
       <c r="BM6" s="4"/>
@@ -2056,7 +2071,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -2222,7 +2237,9 @@
       <c r="BI7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ7" s="4"/>
+      <c r="BJ7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK7" s="4"/>
       <c r="BL7" s="4"/>
       <c r="BM7" s="4"/>
@@ -2285,7 +2302,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2469,7 +2486,9 @@
       <c r="BI8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="BJ8" s="4"/>
+      <c r="BJ8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK8" s="4"/>
       <c r="BL8" s="4"/>
       <c r="BM8" s="4"/>
@@ -2532,7 +2551,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2716,7 +2735,9 @@
       <c r="BI9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ9" s="4"/>
+      <c r="BJ9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK9" s="4"/>
       <c r="BL9" s="4"/>
       <c r="BM9" s="4"/>
@@ -2779,7 +2800,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -2963,7 +2984,9 @@
       <c r="BI10" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="BJ10" s="4"/>
+      <c r="BJ10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK10" s="4"/>
       <c r="BL10" s="4"/>
       <c r="BM10" s="4"/>
@@ -3026,7 +3049,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -3210,7 +3233,9 @@
       <c r="BI11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ11" s="4"/>
+      <c r="BJ11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK11" s="4"/>
       <c r="BL11" s="4"/>
       <c r="BM11" s="4"/>
@@ -3273,7 +3298,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -3457,7 +3482,9 @@
       <c r="BI12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ12" s="4"/>
+      <c r="BJ12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK12" s="4"/>
       <c r="BL12" s="4"/>
       <c r="BM12" s="4"/>
@@ -3520,7 +3547,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -3695,7 +3722,9 @@
       <c r="BI13" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="BJ13" s="4"/>
+      <c r="BJ13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK13" s="4"/>
       <c r="BL13" s="4"/>
       <c r="BM13" s="4"/>
@@ -3758,7 +3787,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -3942,7 +3971,9 @@
       <c r="BI14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ14" s="4"/>
+      <c r="BJ14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK14" s="4"/>
       <c r="BL14" s="4"/>
       <c r="BM14" s="4"/>
@@ -4005,7 +4036,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -4189,7 +4220,9 @@
       <c r="BI15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ15" s="4"/>
+      <c r="BJ15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK15" s="4"/>
       <c r="BL15" s="4"/>
       <c r="BM15" s="4"/>
@@ -4252,7 +4285,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -4481,7 +4514,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -4665,7 +4698,9 @@
       <c r="BI17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ17" s="4"/>
+      <c r="BJ17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK17" s="4"/>
       <c r="BL17" s="4"/>
       <c r="BM17" s="4"/>
@@ -4728,7 +4763,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -4912,7 +4947,9 @@
       <c r="BI18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ18" s="4"/>
+      <c r="BJ18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK18" s="4"/>
       <c r="BL18" s="4"/>
       <c r="BM18" s="4"/>
@@ -4975,7 +5012,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -5204,7 +5241,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -5388,7 +5425,9 @@
       <c r="BI20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ20" s="4"/>
+      <c r="BJ20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK20" s="4"/>
       <c r="BL20" s="4"/>
       <c r="BM20" s="4"/>
@@ -5451,7 +5490,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -5635,7 +5674,9 @@
       <c r="BI21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ21" s="4"/>
+      <c r="BJ21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK21" s="4"/>
       <c r="BL21" s="4"/>
       <c r="BM21" s="4"/>
@@ -5698,7 +5739,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -5882,7 +5923,9 @@
       <c r="BI22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ22" s="4"/>
+      <c r="BJ22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK22" s="4"/>
       <c r="BL22" s="4"/>
       <c r="BM22" s="4"/>
@@ -5945,7 +5988,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -6129,7 +6172,9 @@
       <c r="BI23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ23" s="4"/>
+      <c r="BJ23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK23" s="4"/>
       <c r="BL23" s="4"/>
       <c r="BM23" s="4"/>
@@ -6192,7 +6237,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -6355,7 +6400,9 @@
       <c r="BI24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ24" s="4"/>
+      <c r="BJ24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK24" s="4"/>
       <c r="BL24" s="4"/>
       <c r="BM24" s="4"/>
@@ -6418,7 +6465,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -6602,7 +6649,9 @@
       <c r="BI25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ25" s="4"/>
+      <c r="BJ25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK25" s="4"/>
       <c r="BL25" s="4"/>
       <c r="BM25" s="4"/>
@@ -6665,7 +6714,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -6849,7 +6898,9 @@
       <c r="BI26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ26" s="4"/>
+      <c r="BJ26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK26" s="4"/>
       <c r="BL26" s="4"/>
       <c r="BM26" s="4"/>
@@ -6912,7 +6963,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -7096,7 +7147,9 @@
       <c r="BI27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ27" s="4"/>
+      <c r="BJ27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK27" s="4"/>
       <c r="BL27" s="4"/>
       <c r="BM27" s="4"/>
@@ -7159,7 +7212,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -7343,7 +7396,9 @@
       <c r="BI28" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BJ28" s="4"/>
+      <c r="BJ28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK28" s="4"/>
       <c r="BL28" s="4"/>
       <c r="BM28" s="4"/>
@@ -7406,7 +7461,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -7590,7 +7645,9 @@
       <c r="BI29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ29" s="4"/>
+      <c r="BJ29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK29" s="4"/>
       <c r="BL29" s="4"/>
       <c r="BM29" s="4"/>
@@ -7653,7 +7710,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -7837,7 +7894,9 @@
       <c r="BI30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ30" s="4"/>
+      <c r="BJ30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK30" s="4"/>
       <c r="BL30" s="4"/>
       <c r="BM30" s="4"/>
@@ -7900,7 +7959,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -8084,7 +8143,9 @@
       <c r="BI31" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="BJ31" s="4"/>
+      <c r="BJ31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK31" s="4"/>
       <c r="BL31" s="4"/>
       <c r="BM31" s="4"/>
@@ -8147,7 +8208,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -8331,13 +8392,15 @@
       <c r="BI32" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BJ32" s="4"/>
+      <c r="BJ32" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK32" s="4"/>
       <c r="BL32" s="4"/>
       <c r="BM32" s="4"/>
       <c r="BN32" s="4"/>
     </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -8521,13 +8584,15 @@
       <c r="BI33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ33" s="4"/>
+      <c r="BJ33" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK33" s="4"/>
       <c r="BL33" s="4"/>
       <c r="BM33" s="4"/>
       <c r="BN33" s="4"/>
     </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -8711,7 +8776,9 @@
       <c r="BI34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BJ34" s="4"/>
+      <c r="BJ34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BK34" s="4"/>
       <c r="BL34" s="4"/>
       <c r="BM34" s="4"/>
@@ -8755,13 +8822,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8769,7 +8836,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -8777,7 +8844,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -8785,7 +8852,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -8793,7 +8860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -8801,7 +8868,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -8809,7 +8876,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -8817,7 +8884,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -8825,7 +8892,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -8833,7 +8900,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -8841,7 +8908,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -8849,7 +8916,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -8857,7 +8924,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -8865,7 +8932,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -8873,7 +8940,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -8881,7 +8948,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -8889,7 +8956,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -8897,7 +8964,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -8905,7 +8972,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -8913,7 +8980,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -8921,7 +8988,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -8929,7 +8996,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -8937,7 +9004,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -8945,7 +9012,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -8953,7 +9020,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -8961,7 +9028,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -8969,7 +9036,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -8977,7 +9044,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -8985,7 +9052,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -8993,7 +9060,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -9001,7 +9068,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -9009,7 +9076,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -9017,7 +9084,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F5EDE8-3892-449B-80F3-2DAE790CD2CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC85771E-093E-4287-B4B3-547CF2632298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1982" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="52">
   <si>
     <t>TER</t>
   </si>
@@ -826,8 +826,12 @@
       <c r="BK1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="BL1" s="1"/>
-      <c r="BM1" s="1"/>
+      <c r="BL1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="BN1" s="3"/>
       <c r="BO1" s="3"/>
       <c r="BP1" s="3"/>
@@ -1046,8 +1050,12 @@
       <c r="BK2" s="1">
         <v>46282</v>
       </c>
-      <c r="BL2" s="1"/>
-      <c r="BM2" s="1"/>
+      <c r="BL2" s="1">
+        <v>46287</v>
+      </c>
+      <c r="BM2" s="1">
+        <v>46289</v>
+      </c>
       <c r="BN2" s="4"/>
       <c r="BO2" s="4"/>
       <c r="BP2" s="4"/>
@@ -1262,8 +1270,12 @@
       <c r="BJ3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK3" s="4"/>
-      <c r="BL3" s="4"/>
+      <c r="BK3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM3" s="4"/>
       <c r="BN3" s="4"/>
       <c r="BO3" s="4"/>
@@ -1511,8 +1523,12 @@
       <c r="BJ4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK4" s="4"/>
-      <c r="BL4" s="4"/>
+      <c r="BK4" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM4" s="4"/>
       <c r="BN4" s="4"/>
       <c r="BO4" s="4"/>
@@ -1760,8 +1776,12 @@
       <c r="BJ5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK5" s="4"/>
-      <c r="BL5" s="4"/>
+      <c r="BK5" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM5" s="4"/>
       <c r="BN5" s="4"/>
       <c r="BO5" s="4"/>
@@ -2009,8 +2029,12 @@
       <c r="BJ6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK6" s="4"/>
-      <c r="BL6" s="4"/>
+      <c r="BK6" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM6" s="4"/>
       <c r="BN6" s="4"/>
       <c r="BO6" s="4"/>
@@ -2240,8 +2264,12 @@
       <c r="BJ7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK7" s="4"/>
-      <c r="BL7" s="4"/>
+      <c r="BK7" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM7" s="4"/>
       <c r="BN7" s="4"/>
       <c r="BO7" s="4"/>
@@ -2489,8 +2517,12 @@
       <c r="BJ8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK8" s="4"/>
-      <c r="BL8" s="4"/>
+      <c r="BK8" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM8" s="4"/>
       <c r="BN8" s="4"/>
       <c r="BO8" s="4"/>
@@ -2738,8 +2770,12 @@
       <c r="BJ9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK9" s="4"/>
-      <c r="BL9" s="4"/>
+      <c r="BK9" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM9" s="4"/>
       <c r="BN9" s="4"/>
       <c r="BO9" s="4"/>
@@ -2987,8 +3023,12 @@
       <c r="BJ10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK10" s="4"/>
-      <c r="BL10" s="4"/>
+      <c r="BK10" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM10" s="4"/>
       <c r="BN10" s="4"/>
       <c r="BO10" s="4"/>
@@ -3236,8 +3276,12 @@
       <c r="BJ11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK11" s="4"/>
-      <c r="BL11" s="4"/>
+      <c r="BK11" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM11" s="4"/>
       <c r="BN11" s="4"/>
       <c r="BO11" s="4"/>
@@ -3485,8 +3529,12 @@
       <c r="BJ12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK12" s="4"/>
-      <c r="BL12" s="4"/>
+      <c r="BK12" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM12" s="4"/>
       <c r="BN12" s="4"/>
       <c r="BO12" s="4"/>
@@ -3725,8 +3773,12 @@
       <c r="BJ13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK13" s="4"/>
-      <c r="BL13" s="4"/>
+      <c r="BK13" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM13" s="4"/>
       <c r="BN13" s="4"/>
       <c r="BO13" s="4"/>
@@ -3974,8 +4026,12 @@
       <c r="BJ14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK14" s="4"/>
-      <c r="BL14" s="4"/>
+      <c r="BK14" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM14" s="4"/>
       <c r="BN14" s="4"/>
       <c r="BO14" s="4"/>
@@ -4223,8 +4279,12 @@
       <c r="BJ15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK15" s="4"/>
-      <c r="BL15" s="4"/>
+      <c r="BK15" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM15" s="4"/>
       <c r="BN15" s="4"/>
       <c r="BO15" s="4"/>
@@ -4452,8 +4512,12 @@
       </c>
       <c r="BI16" s="4"/>
       <c r="BJ16" s="4"/>
-      <c r="BK16" s="4"/>
-      <c r="BL16" s="4"/>
+      <c r="BK16" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL16" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM16" s="4"/>
       <c r="BN16" s="4"/>
       <c r="BO16" s="4"/>
@@ -4701,8 +4765,12 @@
       <c r="BJ17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK17" s="4"/>
-      <c r="BL17" s="4"/>
+      <c r="BK17" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM17" s="4"/>
       <c r="BN17" s="4"/>
       <c r="BO17" s="4"/>
@@ -4950,8 +5018,12 @@
       <c r="BJ18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK18" s="4"/>
-      <c r="BL18" s="4"/>
+      <c r="BK18" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM18" s="4"/>
       <c r="BN18" s="4"/>
       <c r="BO18" s="4"/>
@@ -5179,8 +5251,12 @@
       </c>
       <c r="BI19" s="4"/>
       <c r="BJ19" s="4"/>
-      <c r="BK19" s="4"/>
-      <c r="BL19" s="4"/>
+      <c r="BK19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL19" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM19" s="4"/>
       <c r="BN19" s="4"/>
       <c r="BO19" s="4"/>
@@ -5428,8 +5504,12 @@
       <c r="BJ20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK20" s="4"/>
-      <c r="BL20" s="4"/>
+      <c r="BK20" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM20" s="4"/>
       <c r="BN20" s="4"/>
       <c r="BO20" s="4"/>
@@ -5677,8 +5757,12 @@
       <c r="BJ21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK21" s="4"/>
-      <c r="BL21" s="4"/>
+      <c r="BK21" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM21" s="4"/>
       <c r="BN21" s="4"/>
       <c r="BO21" s="4"/>
@@ -5926,8 +6010,12 @@
       <c r="BJ22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK22" s="4"/>
-      <c r="BL22" s="4"/>
+      <c r="BK22" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM22" s="4"/>
       <c r="BN22" s="4"/>
       <c r="BO22" s="4"/>
@@ -6175,8 +6263,12 @@
       <c r="BJ23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK23" s="4"/>
-      <c r="BL23" s="4"/>
+      <c r="BK23" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL23" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BM23" s="4"/>
       <c r="BN23" s="4"/>
       <c r="BO23" s="4"/>
@@ -6403,8 +6495,12 @@
       <c r="BJ24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK24" s="4"/>
-      <c r="BL24" s="4"/>
+      <c r="BK24" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM24" s="4"/>
       <c r="BN24" s="4"/>
       <c r="BO24" s="4"/>
@@ -6652,8 +6748,12 @@
       <c r="BJ25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK25" s="4"/>
-      <c r="BL25" s="4"/>
+      <c r="BK25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM25" s="4"/>
       <c r="BN25" s="4"/>
       <c r="BO25" s="4"/>
@@ -6901,8 +7001,12 @@
       <c r="BJ26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK26" s="4"/>
-      <c r="BL26" s="4"/>
+      <c r="BK26" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM26" s="4"/>
       <c r="BN26" s="4"/>
       <c r="BO26" s="4"/>
@@ -7150,8 +7254,12 @@
       <c r="BJ27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK27" s="4"/>
-      <c r="BL27" s="4"/>
+      <c r="BK27" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM27" s="4"/>
       <c r="BN27" s="4"/>
       <c r="BO27" s="4"/>
@@ -7399,8 +7507,12 @@
       <c r="BJ28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK28" s="4"/>
-      <c r="BL28" s="4"/>
+      <c r="BK28" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM28" s="4"/>
       <c r="BN28" s="4"/>
       <c r="BO28" s="4"/>
@@ -7648,8 +7760,12 @@
       <c r="BJ29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK29" s="4"/>
-      <c r="BL29" s="4"/>
+      <c r="BK29" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM29" s="4"/>
       <c r="BN29" s="4"/>
       <c r="BO29" s="4"/>
@@ -7897,8 +8013,12 @@
       <c r="BJ30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK30" s="4"/>
-      <c r="BL30" s="4"/>
+      <c r="BK30" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM30" s="4"/>
       <c r="BN30" s="4"/>
       <c r="BO30" s="4"/>
@@ -8146,8 +8266,12 @@
       <c r="BJ31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK31" s="4"/>
-      <c r="BL31" s="4"/>
+      <c r="BK31" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM31" s="4"/>
       <c r="BN31" s="4"/>
       <c r="BO31" s="4"/>
@@ -8395,8 +8519,12 @@
       <c r="BJ32" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK32" s="4"/>
-      <c r="BL32" s="4"/>
+      <c r="BK32" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL32" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM32" s="4"/>
       <c r="BN32" s="4"/>
     </row>
@@ -8587,8 +8715,12 @@
       <c r="BJ33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK33" s="4"/>
-      <c r="BL33" s="4"/>
+      <c r="BK33" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL33" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM33" s="4"/>
       <c r="BN33" s="4"/>
     </row>
@@ -8779,8 +8911,12 @@
       <c r="BJ34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BK34" s="4"/>
-      <c r="BL34" s="4"/>
+      <c r="BK34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BL34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BM34" s="4"/>
       <c r="BN34" s="4"/>
     </row>
@@ -8789,7 +8925,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:BG31 BI3:DG31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BD11:BE31 AZ23:BB31 G32:I32 AV32:AV34">
+  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:BG31 BI3:DG4 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BD11:BE31 AZ23:BB31 G32:I32 AV32:AV34 BI5:BJ31 BL5:DG12 BK5:BK34 BM13:DG31 BL13:BL34">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC85771E-093E-4287-B4B3-547CF2632298}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB938254-3703-448D-9AC9-A70EA8251092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="53">
   <si>
     <t>TER</t>
   </si>
@@ -193,6 +193,9 @@
   </si>
   <si>
     <t>5P/F</t>
+  </si>
+  <si>
+    <t>P/8</t>
   </si>
 </sst>
 </file>
@@ -616,36 +619,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="39" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.6640625" customWidth="1"/>
-    <col min="42" max="46" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="39" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.7109375" customWidth="1"/>
+    <col min="42" max="46" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="7" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="7" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="7" style="4" bestFit="1" customWidth="1"/>
     <col min="52" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="59" width="7.6640625" customWidth="1"/>
-    <col min="60" max="60" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="61" max="106" width="7.6640625" customWidth="1"/>
+    <col min="55" max="59" width="7.7109375" customWidth="1"/>
+    <col min="60" max="60" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="61" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -859,7 +862,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1083,7 +1086,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1276,7 +1279,9 @@
       <c r="BL3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM3" s="4"/>
+      <c r="BM3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN3" s="4"/>
       <c r="BO3" s="4"/>
       <c r="BP3" s="4"/>
@@ -1336,7 +1341,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1529,7 +1534,9 @@
       <c r="BL4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM4" s="4"/>
+      <c r="BM4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN4" s="4"/>
       <c r="BO4" s="4"/>
       <c r="BP4" s="4"/>
@@ -1589,7 +1596,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1782,7 +1789,9 @@
       <c r="BL5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM5" s="4"/>
+      <c r="BM5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN5" s="4"/>
       <c r="BO5" s="4"/>
       <c r="BP5" s="4"/>
@@ -1842,7 +1851,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -2035,7 +2044,9 @@
       <c r="BL6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM6" s="4"/>
+      <c r="BM6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN6" s="4"/>
       <c r="BO6" s="4"/>
       <c r="BP6" s="4"/>
@@ -2095,7 +2106,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -2270,7 +2281,9 @@
       <c r="BL7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM7" s="4"/>
+      <c r="BM7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN7" s="4"/>
       <c r="BO7" s="4"/>
       <c r="BP7" s="4"/>
@@ -2330,7 +2343,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2523,7 +2536,9 @@
       <c r="BL8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM8" s="4"/>
+      <c r="BM8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN8" s="4"/>
       <c r="BO8" s="4"/>
       <c r="BP8" s="4"/>
@@ -2583,7 +2598,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2776,7 +2791,9 @@
       <c r="BL9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM9" s="4"/>
+      <c r="BM9" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="BN9" s="4"/>
       <c r="BO9" s="4"/>
       <c r="BP9" s="4"/>
@@ -2836,7 +2853,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -3029,7 +3046,9 @@
       <c r="BL10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM10" s="4"/>
+      <c r="BM10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN10" s="4"/>
       <c r="BO10" s="4"/>
       <c r="BP10" s="4"/>
@@ -3089,7 +3108,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -3282,7 +3301,9 @@
       <c r="BL11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM11" s="4"/>
+      <c r="BM11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN11" s="4"/>
       <c r="BO11" s="4"/>
       <c r="BP11" s="4"/>
@@ -3342,7 +3363,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -3535,7 +3556,9 @@
       <c r="BL12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM12" s="4"/>
+      <c r="BM12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN12" s="4"/>
       <c r="BO12" s="4"/>
       <c r="BP12" s="4"/>
@@ -3595,7 +3618,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -3779,7 +3802,9 @@
       <c r="BL13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM13" s="4"/>
+      <c r="BM13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN13" s="4"/>
       <c r="BO13" s="4"/>
       <c r="BP13" s="4"/>
@@ -3839,7 +3864,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -4032,7 +4057,9 @@
       <c r="BL14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM14" s="4"/>
+      <c r="BM14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN14" s="4"/>
       <c r="BO14" s="4"/>
       <c r="BP14" s="4"/>
@@ -4092,7 +4119,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -4285,7 +4312,9 @@
       <c r="BL15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM15" s="4"/>
+      <c r="BM15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN15" s="4"/>
       <c r="BO15" s="4"/>
       <c r="BP15" s="4"/>
@@ -4345,7 +4374,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -4578,7 +4607,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -4771,7 +4800,9 @@
       <c r="BL17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM17" s="4"/>
+      <c r="BM17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN17" s="4"/>
       <c r="BO17" s="4"/>
       <c r="BP17" s="4"/>
@@ -4831,7 +4862,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -5024,7 +5055,9 @@
       <c r="BL18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM18" s="4"/>
+      <c r="BM18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN18" s="4"/>
       <c r="BO18" s="4"/>
       <c r="BP18" s="4"/>
@@ -5084,7 +5117,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -5317,7 +5350,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -5510,7 +5543,9 @@
       <c r="BL20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM20" s="4"/>
+      <c r="BM20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN20" s="4"/>
       <c r="BO20" s="4"/>
       <c r="BP20" s="4"/>
@@ -5570,7 +5605,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -5763,7 +5798,9 @@
       <c r="BL21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM21" s="4"/>
+      <c r="BM21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN21" s="4"/>
       <c r="BO21" s="4"/>
       <c r="BP21" s="4"/>
@@ -5823,7 +5860,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -6016,7 +6053,9 @@
       <c r="BL22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM22" s="4"/>
+      <c r="BM22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN22" s="4"/>
       <c r="BO22" s="4"/>
       <c r="BP22" s="4"/>
@@ -6076,7 +6115,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -6269,7 +6308,9 @@
       <c r="BL23" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BM23" s="4"/>
+      <c r="BM23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN23" s="4"/>
       <c r="BO23" s="4"/>
       <c r="BP23" s="4"/>
@@ -6329,7 +6370,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -6501,7 +6542,9 @@
       <c r="BL24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM24" s="4"/>
+      <c r="BM24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN24" s="4"/>
       <c r="BO24" s="4"/>
       <c r="BP24" s="4"/>
@@ -6561,7 +6604,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -6754,7 +6797,9 @@
       <c r="BL25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM25" s="4"/>
+      <c r="BM25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN25" s="4"/>
       <c r="BO25" s="4"/>
       <c r="BP25" s="4"/>
@@ -6814,7 +6859,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -7007,7 +7052,9 @@
       <c r="BL26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM26" s="4"/>
+      <c r="BM26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN26" s="4"/>
       <c r="BO26" s="4"/>
       <c r="BP26" s="4"/>
@@ -7067,7 +7114,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -7260,7 +7307,9 @@
       <c r="BL27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM27" s="4"/>
+      <c r="BM27" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="BN27" s="4"/>
       <c r="BO27" s="4"/>
       <c r="BP27" s="4"/>
@@ -7320,7 +7369,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -7513,7 +7562,9 @@
       <c r="BL28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM28" s="4"/>
+      <c r="BM28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN28" s="4"/>
       <c r="BO28" s="4"/>
       <c r="BP28" s="4"/>
@@ -7573,7 +7624,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -7766,7 +7817,9 @@
       <c r="BL29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM29" s="4"/>
+      <c r="BM29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN29" s="4"/>
       <c r="BO29" s="4"/>
       <c r="BP29" s="4"/>
@@ -7826,7 +7879,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -8019,7 +8072,9 @@
       <c r="BL30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM30" s="4"/>
+      <c r="BM30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN30" s="4"/>
       <c r="BO30" s="4"/>
       <c r="BP30" s="4"/>
@@ -8079,7 +8134,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -8272,7 +8327,9 @@
       <c r="BL31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM31" s="4"/>
+      <c r="BM31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN31" s="4"/>
       <c r="BO31" s="4"/>
       <c r="BP31" s="4"/>
@@ -8332,7 +8389,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -8525,10 +8582,12 @@
       <c r="BL32" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM32" s="4"/>
+      <c r="BM32" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN32" s="4"/>
     </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -8721,10 +8780,12 @@
       <c r="BL33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM33" s="4"/>
+      <c r="BM33" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN33" s="4"/>
     </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -8917,7 +8978,9 @@
       <c r="BL34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BM34" s="4"/>
+      <c r="BM34" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BN34" s="4"/>
     </row>
   </sheetData>
@@ -8925,7 +8988,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:BG31 BI3:DG4 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 AV5:AX31 AY5:AY34 AZ11:BA22 BD11:BE31 AZ23:BB31 G32:I32 AV32:AV34 BI5:BJ31 BL5:DG12 BK5:BK34 BM13:DG31 BL13:BL34">
+  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BI3:DG4 BB3:BB22 BC3:BC31 BF3:BG31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 BL5:DG12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:DG31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -8958,13 +9021,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -8972,7 +9035,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -8980,7 +9043,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -8988,7 +9051,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -8996,7 +9059,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -9004,7 +9067,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -9012,7 +9075,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -9020,7 +9083,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -9028,7 +9091,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -9036,7 +9099,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -9044,7 +9107,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -9052,7 +9115,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -9060,7 +9123,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -9068,7 +9131,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -9076,7 +9139,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -9084,7 +9147,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -9092,7 +9155,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -9100,7 +9163,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -9108,7 +9171,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -9116,7 +9179,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -9124,7 +9187,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -9132,7 +9195,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -9140,7 +9203,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -9148,7 +9211,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -9156,7 +9219,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -9164,7 +9227,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -9172,7 +9235,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -9180,7 +9243,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -9188,7 +9251,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -9196,7 +9259,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -9204,7 +9267,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -9212,7 +9275,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -9220,7 +9283,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB938254-3703-448D-9AC9-A70EA8251092}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0784A1D4-CFE9-4D1A-B04A-09F6CE77978A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2110" uniqueCount="53">
   <si>
     <t>TER</t>
   </si>
@@ -619,36 +619,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="39" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.7109375" customWidth="1"/>
-    <col min="42" max="46" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="39" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.6640625" customWidth="1"/>
+    <col min="42" max="46" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="7" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="7" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="7" style="4" bestFit="1" customWidth="1"/>
     <col min="52" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="59" width="7.7109375" customWidth="1"/>
-    <col min="60" max="60" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="61" max="106" width="7.7109375" customWidth="1"/>
+    <col min="55" max="59" width="7.6640625" customWidth="1"/>
+    <col min="60" max="60" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="61" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -835,8 +835,12 @@
       <c r="BM1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="BN1" s="3"/>
-      <c r="BO1" s="3"/>
+      <c r="BN1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="BP1" s="3"/>
       <c r="BQ1" s="3"/>
       <c r="BR1" s="3"/>
@@ -862,7 +866,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1059,8 +1063,12 @@
       <c r="BM2" s="1">
         <v>46289</v>
       </c>
-      <c r="BN2" s="4"/>
-      <c r="BO2" s="4"/>
+      <c r="BN2" s="1">
+        <v>46294</v>
+      </c>
+      <c r="BO2" s="1">
+        <v>46296</v>
+      </c>
       <c r="BP2" s="4"/>
       <c r="BQ2" s="4"/>
       <c r="BR2" s="4"/>
@@ -1086,7 +1094,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1282,7 +1290,9 @@
       <c r="BM3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN3" s="4"/>
+      <c r="BN3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO3" s="4"/>
       <c r="BP3" s="4"/>
       <c r="BQ3" s="4"/>
@@ -1341,7 +1351,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1537,7 +1547,9 @@
       <c r="BM4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN4" s="4"/>
+      <c r="BN4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO4" s="4"/>
       <c r="BP4" s="4"/>
       <c r="BQ4" s="4"/>
@@ -1596,7 +1608,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1792,7 +1804,9 @@
       <c r="BM5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN5" s="4"/>
+      <c r="BN5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO5" s="4"/>
       <c r="BP5" s="4"/>
       <c r="BQ5" s="4"/>
@@ -1851,7 +1865,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -2047,7 +2061,9 @@
       <c r="BM6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN6" s="4"/>
+      <c r="BN6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO6" s="4"/>
       <c r="BP6" s="4"/>
       <c r="BQ6" s="4"/>
@@ -2106,7 +2122,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -2284,7 +2300,9 @@
       <c r="BM7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN7" s="4"/>
+      <c r="BN7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO7" s="4"/>
       <c r="BP7" s="4"/>
       <c r="BQ7" s="4"/>
@@ -2343,7 +2361,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2539,7 +2557,9 @@
       <c r="BM8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN8" s="4"/>
+      <c r="BN8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO8" s="4"/>
       <c r="BP8" s="4"/>
       <c r="BQ8" s="4"/>
@@ -2598,7 +2618,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2794,7 +2814,9 @@
       <c r="BM9" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="BN9" s="4"/>
+      <c r="BN9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO9" s="4"/>
       <c r="BP9" s="4"/>
       <c r="BQ9" s="4"/>
@@ -2853,7 +2875,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -3049,7 +3071,9 @@
       <c r="BM10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN10" s="4"/>
+      <c r="BN10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO10" s="4"/>
       <c r="BP10" s="4"/>
       <c r="BQ10" s="4"/>
@@ -3108,7 +3132,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -3304,7 +3328,9 @@
       <c r="BM11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN11" s="4"/>
+      <c r="BN11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO11" s="4"/>
       <c r="BP11" s="4"/>
       <c r="BQ11" s="4"/>
@@ -3363,7 +3389,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -3559,7 +3585,9 @@
       <c r="BM12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN12" s="4"/>
+      <c r="BN12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO12" s="4"/>
       <c r="BP12" s="4"/>
       <c r="BQ12" s="4"/>
@@ -3618,7 +3646,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -3805,7 +3833,9 @@
       <c r="BM13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN13" s="4"/>
+      <c r="BN13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO13" s="4"/>
       <c r="BP13" s="4"/>
       <c r="BQ13" s="4"/>
@@ -3864,7 +3894,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -4060,7 +4090,9 @@
       <c r="BM14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN14" s="4"/>
+      <c r="BN14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO14" s="4"/>
       <c r="BP14" s="4"/>
       <c r="BQ14" s="4"/>
@@ -4119,7 +4151,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -4315,7 +4347,9 @@
       <c r="BM15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN15" s="4"/>
+      <c r="BN15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO15" s="4"/>
       <c r="BP15" s="4"/>
       <c r="BQ15" s="4"/>
@@ -4374,7 +4408,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -4607,7 +4641,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -4803,7 +4837,9 @@
       <c r="BM17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN17" s="4"/>
+      <c r="BN17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO17" s="4"/>
       <c r="BP17" s="4"/>
       <c r="BQ17" s="4"/>
@@ -4862,7 +4898,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -5058,7 +5094,9 @@
       <c r="BM18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN18" s="4"/>
+      <c r="BN18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO18" s="4"/>
       <c r="BP18" s="4"/>
       <c r="BQ18" s="4"/>
@@ -5117,7 +5155,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -5350,7 +5388,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -5546,7 +5584,9 @@
       <c r="BM20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN20" s="4"/>
+      <c r="BN20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO20" s="4"/>
       <c r="BP20" s="4"/>
       <c r="BQ20" s="4"/>
@@ -5605,7 +5645,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -5801,7 +5841,9 @@
       <c r="BM21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN21" s="4"/>
+      <c r="BN21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO21" s="4"/>
       <c r="BP21" s="4"/>
       <c r="BQ21" s="4"/>
@@ -5860,7 +5902,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -6056,7 +6098,9 @@
       <c r="BM22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN22" s="4"/>
+      <c r="BN22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO22" s="4"/>
       <c r="BP22" s="4"/>
       <c r="BQ22" s="4"/>
@@ -6115,7 +6159,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -6311,7 +6355,9 @@
       <c r="BM23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN23" s="4"/>
+      <c r="BN23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO23" s="4"/>
       <c r="BP23" s="4"/>
       <c r="BQ23" s="4"/>
@@ -6370,7 +6416,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -6545,7 +6591,9 @@
       <c r="BM24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN24" s="4"/>
+      <c r="BN24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO24" s="4"/>
       <c r="BP24" s="4"/>
       <c r="BQ24" s="4"/>
@@ -6604,7 +6652,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -6800,7 +6848,9 @@
       <c r="BM25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN25" s="4"/>
+      <c r="BN25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO25" s="4"/>
       <c r="BP25" s="4"/>
       <c r="BQ25" s="4"/>
@@ -6859,7 +6909,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -7055,7 +7105,9 @@
       <c r="BM26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN26" s="4"/>
+      <c r="BN26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO26" s="4"/>
       <c r="BP26" s="4"/>
       <c r="BQ26" s="4"/>
@@ -7114,7 +7166,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -7310,7 +7362,9 @@
       <c r="BM27" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="BN27" s="4"/>
+      <c r="BN27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO27" s="4"/>
       <c r="BP27" s="4"/>
       <c r="BQ27" s="4"/>
@@ -7369,7 +7423,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -7565,7 +7619,9 @@
       <c r="BM28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN28" s="4"/>
+      <c r="BN28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO28" s="4"/>
       <c r="BP28" s="4"/>
       <c r="BQ28" s="4"/>
@@ -7624,7 +7680,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -7820,7 +7876,9 @@
       <c r="BM29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN29" s="4"/>
+      <c r="BN29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO29" s="4"/>
       <c r="BP29" s="4"/>
       <c r="BQ29" s="4"/>
@@ -7879,7 +7937,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -8075,7 +8133,9 @@
       <c r="BM30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN30" s="4"/>
+      <c r="BN30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO30" s="4"/>
       <c r="BP30" s="4"/>
       <c r="BQ30" s="4"/>
@@ -8134,7 +8194,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -8330,7 +8390,9 @@
       <c r="BM31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN31" s="4"/>
+      <c r="BN31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BO31" s="4"/>
       <c r="BP31" s="4"/>
       <c r="BQ31" s="4"/>
@@ -8389,7 +8451,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -8585,9 +8647,11 @@
       <c r="BM32" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN32" s="4"/>
+      <c r="BN32" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -8783,9 +8847,11 @@
       <c r="BM33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN33" s="4"/>
+      <c r="BN33" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:66" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -8981,7 +9047,9 @@
       <c r="BM34" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BN34" s="4"/>
+      <c r="BN34" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B3:N34">
@@ -9021,13 +9089,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -9035,7 +9103,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -9043,7 +9111,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -9051,7 +9119,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -9059,7 +9127,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -9067,7 +9135,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -9075,7 +9143,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -9083,7 +9151,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -9091,7 +9159,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -9099,7 +9167,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -9107,7 +9175,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -9115,7 +9183,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -9123,7 +9191,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -9131,7 +9199,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -9139,7 +9207,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -9147,7 +9215,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -9155,7 +9223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -9163,7 +9231,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -9171,7 +9239,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -9179,7 +9247,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -9187,7 +9255,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -9195,7 +9263,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -9203,7 +9271,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -9211,7 +9279,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -9219,7 +9287,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -9227,7 +9295,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -9235,7 +9303,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -9243,7 +9311,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -9251,7 +9319,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -9259,7 +9327,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -9267,7 +9335,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -9275,7 +9343,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -9283,7 +9351,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Worldskill\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0784A1D4-CFE9-4D1A-B04A-09F6CE77978A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025C0B43-84FB-4A90-AF36-3998E3BE211B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2110" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2140" uniqueCount="53">
   <si>
     <t>TER</t>
   </si>
@@ -619,36 +619,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="39" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.6640625" customWidth="1"/>
-    <col min="42" max="46" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="39" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.7109375" customWidth="1"/>
+    <col min="42" max="46" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="7" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="7" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="7" style="4" bestFit="1" customWidth="1"/>
     <col min="52" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="59" width="7.6640625" customWidth="1"/>
-    <col min="60" max="60" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="61" max="106" width="7.6640625" customWidth="1"/>
+    <col min="55" max="59" width="7.7109375" customWidth="1"/>
+    <col min="60" max="60" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="61" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -866,7 +866,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1094,7 +1094,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1293,7 +1293,9 @@
       <c r="BN3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO3" s="4"/>
+      <c r="BO3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP3" s="4"/>
       <c r="BQ3" s="4"/>
       <c r="BR3" s="4"/>
@@ -1351,7 +1353,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1550,7 +1552,9 @@
       <c r="BN4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO4" s="4"/>
+      <c r="BO4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP4" s="4"/>
       <c r="BQ4" s="4"/>
       <c r="BR4" s="4"/>
@@ -1608,7 +1612,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1807,7 +1811,9 @@
       <c r="BN5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO5" s="4"/>
+      <c r="BO5" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BP5" s="4"/>
       <c r="BQ5" s="4"/>
       <c r="BR5" s="4"/>
@@ -1865,7 +1871,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -2064,7 +2070,9 @@
       <c r="BN6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO6" s="4"/>
+      <c r="BO6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP6" s="4"/>
       <c r="BQ6" s="4"/>
       <c r="BR6" s="4"/>
@@ -2122,7 +2130,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -2303,7 +2311,9 @@
       <c r="BN7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO7" s="4"/>
+      <c r="BO7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP7" s="4"/>
       <c r="BQ7" s="4"/>
       <c r="BR7" s="4"/>
@@ -2361,7 +2371,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2560,7 +2570,9 @@
       <c r="BN8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO8" s="4"/>
+      <c r="BO8" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BP8" s="4"/>
       <c r="BQ8" s="4"/>
       <c r="BR8" s="4"/>
@@ -2618,7 +2630,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2817,7 +2829,9 @@
       <c r="BN9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO9" s="4"/>
+      <c r="BO9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP9" s="4"/>
       <c r="BQ9" s="4"/>
       <c r="BR9" s="4"/>
@@ -2875,7 +2889,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -3074,7 +3088,9 @@
       <c r="BN10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO10" s="4"/>
+      <c r="BO10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP10" s="4"/>
       <c r="BQ10" s="4"/>
       <c r="BR10" s="4"/>
@@ -3132,7 +3148,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -3331,7 +3347,9 @@
       <c r="BN11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO11" s="4"/>
+      <c r="BO11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP11" s="4"/>
       <c r="BQ11" s="4"/>
       <c r="BR11" s="4"/>
@@ -3389,7 +3407,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -3588,7 +3606,9 @@
       <c r="BN12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO12" s="4"/>
+      <c r="BO12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP12" s="4"/>
       <c r="BQ12" s="4"/>
       <c r="BR12" s="4"/>
@@ -3646,7 +3666,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -3836,7 +3856,9 @@
       <c r="BN13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO13" s="4"/>
+      <c r="BO13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP13" s="4"/>
       <c r="BQ13" s="4"/>
       <c r="BR13" s="4"/>
@@ -3894,7 +3916,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -4093,7 +4115,9 @@
       <c r="BN14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO14" s="4"/>
+      <c r="BO14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP14" s="4"/>
       <c r="BQ14" s="4"/>
       <c r="BR14" s="4"/>
@@ -4151,7 +4175,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -4350,7 +4374,9 @@
       <c r="BN15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO15" s="4"/>
+      <c r="BO15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP15" s="4"/>
       <c r="BQ15" s="4"/>
       <c r="BR15" s="4"/>
@@ -4408,7 +4434,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -4641,7 +4667,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -4840,7 +4866,9 @@
       <c r="BN17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO17" s="4"/>
+      <c r="BO17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP17" s="4"/>
       <c r="BQ17" s="4"/>
       <c r="BR17" s="4"/>
@@ -4898,7 +4926,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -5097,7 +5125,9 @@
       <c r="BN18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO18" s="4"/>
+      <c r="BO18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP18" s="4"/>
       <c r="BQ18" s="4"/>
       <c r="BR18" s="4"/>
@@ -5155,7 +5185,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -5388,7 +5418,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -5587,7 +5617,9 @@
       <c r="BN20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO20" s="4"/>
+      <c r="BO20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP20" s="4"/>
       <c r="BQ20" s="4"/>
       <c r="BR20" s="4"/>
@@ -5645,7 +5677,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -5844,7 +5876,9 @@
       <c r="BN21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO21" s="4"/>
+      <c r="BO21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP21" s="4"/>
       <c r="BQ21" s="4"/>
       <c r="BR21" s="4"/>
@@ -5902,7 +5936,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -6101,7 +6135,9 @@
       <c r="BN22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO22" s="4"/>
+      <c r="BO22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP22" s="4"/>
       <c r="BQ22" s="4"/>
       <c r="BR22" s="4"/>
@@ -6159,7 +6195,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -6358,7 +6394,9 @@
       <c r="BN23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO23" s="4"/>
+      <c r="BO23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP23" s="4"/>
       <c r="BQ23" s="4"/>
       <c r="BR23" s="4"/>
@@ -6416,7 +6454,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -6594,7 +6632,9 @@
       <c r="BN24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO24" s="4"/>
+      <c r="BO24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP24" s="4"/>
       <c r="BQ24" s="4"/>
       <c r="BR24" s="4"/>
@@ -6652,7 +6692,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -6851,7 +6891,9 @@
       <c r="BN25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO25" s="4"/>
+      <c r="BO25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP25" s="4"/>
       <c r="BQ25" s="4"/>
       <c r="BR25" s="4"/>
@@ -6909,7 +6951,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -7108,7 +7150,9 @@
       <c r="BN26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO26" s="4"/>
+      <c r="BO26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP26" s="4"/>
       <c r="BQ26" s="4"/>
       <c r="BR26" s="4"/>
@@ -7166,7 +7210,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -7365,7 +7409,9 @@
       <c r="BN27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO27" s="4"/>
+      <c r="BO27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP27" s="4"/>
       <c r="BQ27" s="4"/>
       <c r="BR27" s="4"/>
@@ -7423,7 +7469,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -7622,7 +7668,9 @@
       <c r="BN28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO28" s="4"/>
+      <c r="BO28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP28" s="4"/>
       <c r="BQ28" s="4"/>
       <c r="BR28" s="4"/>
@@ -7680,7 +7728,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -7879,7 +7927,9 @@
       <c r="BN29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO29" s="4"/>
+      <c r="BO29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP29" s="4"/>
       <c r="BQ29" s="4"/>
       <c r="BR29" s="4"/>
@@ -7937,7 +7987,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -8136,7 +8186,9 @@
       <c r="BN30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO30" s="4"/>
+      <c r="BO30" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BP30" s="4"/>
       <c r="BQ30" s="4"/>
       <c r="BR30" s="4"/>
@@ -8194,7 +8246,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -8393,7 +8445,9 @@
       <c r="BN31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BO31" s="4"/>
+      <c r="BO31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BP31" s="4"/>
       <c r="BQ31" s="4"/>
       <c r="BR31" s="4"/>
@@ -8451,7 +8505,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -8650,8 +8704,11 @@
       <c r="BN32" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="BO32" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -8850,8 +8907,11 @@
       <c r="BN33" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="BO33" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="34" spans="1:66" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:67" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -9048,6 +9108,9 @@
         <v>5</v>
       </c>
       <c r="BN34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BO34" s="4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -9056,7 +9119,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BI3:DG4 BB3:BB22 BC3:BC31 BF3:BG31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 BL5:DG12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:DG31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34">
+  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BI3:DG4 BB3:BB22 BC3:BC31 BF3:BG31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 BL5:DG12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:DG31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34 BO32:BO34">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -9089,13 +9152,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -9103,7 +9166,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -9111,7 +9174,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -9119,7 +9182,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -9127,7 +9190,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -9135,7 +9198,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -9143,7 +9206,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -9151,7 +9214,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -9159,7 +9222,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -9167,7 +9230,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -9175,7 +9238,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -9183,7 +9246,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -9191,7 +9254,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -9199,7 +9262,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -9207,7 +9270,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -9215,7 +9278,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -9223,7 +9286,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -9231,7 +9294,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -9239,7 +9302,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -9247,7 +9310,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -9255,7 +9318,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -9263,7 +9326,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -9271,7 +9334,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -9279,7 +9342,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -9287,7 +9350,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -9295,7 +9358,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -9303,7 +9366,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -9311,7 +9374,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -9319,7 +9382,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -9327,7 +9390,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -9335,7 +9398,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -9343,7 +9406,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -9351,7 +9414,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1053361\Documents\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025C0B43-84FB-4A90-AF36-3998E3BE211B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20C03C9-7E11-48DD-B1BF-F15661B700B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2140" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="53">
   <si>
     <t>TER</t>
   </si>
@@ -619,36 +619,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="39" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.7109375" customWidth="1"/>
-    <col min="42" max="46" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="32" max="39" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.6640625" customWidth="1"/>
+    <col min="42" max="46" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="7" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="6.109375" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="7" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="7" style="4" bestFit="1" customWidth="1"/>
     <col min="52" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="59" width="7.7109375" customWidth="1"/>
-    <col min="60" max="60" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="61" max="106" width="7.7109375" customWidth="1"/>
+    <col min="55" max="59" width="7.6640625" customWidth="1"/>
+    <col min="60" max="60" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="61" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -841,8 +841,12 @@
       <c r="BO1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="BP1" s="3"/>
-      <c r="BQ1" s="3"/>
+      <c r="BP1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="BQ1" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="BR1" s="3"/>
       <c r="BS1" s="3"/>
       <c r="BT1" s="3"/>
@@ -866,7 +870,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1069,8 +1073,12 @@
       <c r="BO2" s="1">
         <v>46296</v>
       </c>
-      <c r="BP2" s="4"/>
-      <c r="BQ2" s="4"/>
+      <c r="BP2" s="1">
+        <v>46301</v>
+      </c>
+      <c r="BQ2" s="1">
+        <v>46303</v>
+      </c>
       <c r="BR2" s="4"/>
       <c r="BS2" s="4"/>
       <c r="BT2" s="4"/>
@@ -1094,7 +1102,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1296,7 +1304,9 @@
       <c r="BO3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP3" s="4"/>
+      <c r="BP3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ3" s="4"/>
       <c r="BR3" s="4"/>
       <c r="BS3" s="4"/>
@@ -1353,7 +1363,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1555,7 +1565,9 @@
       <c r="BO4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP4" s="4"/>
+      <c r="BP4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ4" s="4"/>
       <c r="BR4" s="4"/>
       <c r="BS4" s="4"/>
@@ -1612,7 +1624,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1814,7 +1826,9 @@
       <c r="BO5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BP5" s="4"/>
+      <c r="BP5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ5" s="4"/>
       <c r="BR5" s="4"/>
       <c r="BS5" s="4"/>
@@ -1871,7 +1885,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -2073,7 +2087,9 @@
       <c r="BO6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP6" s="4"/>
+      <c r="BP6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ6" s="4"/>
       <c r="BR6" s="4"/>
       <c r="BS6" s="4"/>
@@ -2130,7 +2146,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -2314,7 +2330,9 @@
       <c r="BO7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP7" s="4"/>
+      <c r="BP7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ7" s="4"/>
       <c r="BR7" s="4"/>
       <c r="BS7" s="4"/>
@@ -2371,7 +2389,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2573,7 +2591,9 @@
       <c r="BO8" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BP8" s="4"/>
+      <c r="BP8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ8" s="4"/>
       <c r="BR8" s="4"/>
       <c r="BS8" s="4"/>
@@ -2630,7 +2650,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2832,7 +2852,9 @@
       <c r="BO9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP9" s="4"/>
+      <c r="BP9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ9" s="4"/>
       <c r="BR9" s="4"/>
       <c r="BS9" s="4"/>
@@ -2889,7 +2911,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -3091,7 +3113,9 @@
       <c r="BO10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP10" s="4"/>
+      <c r="BP10" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BQ10" s="4"/>
       <c r="BR10" s="4"/>
       <c r="BS10" s="4"/>
@@ -3148,7 +3172,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -3350,7 +3374,9 @@
       <c r="BO11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP11" s="4"/>
+      <c r="BP11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ11" s="4"/>
       <c r="BR11" s="4"/>
       <c r="BS11" s="4"/>
@@ -3407,7 +3433,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -3609,7 +3635,9 @@
       <c r="BO12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP12" s="4"/>
+      <c r="BP12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ12" s="4"/>
       <c r="BR12" s="4"/>
       <c r="BS12" s="4"/>
@@ -3666,7 +3694,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -3859,7 +3887,9 @@
       <c r="BO13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP13" s="4"/>
+      <c r="BP13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ13" s="4"/>
       <c r="BR13" s="4"/>
       <c r="BS13" s="4"/>
@@ -3916,7 +3946,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -4118,7 +4148,9 @@
       <c r="BO14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP14" s="4"/>
+      <c r="BP14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ14" s="4"/>
       <c r="BR14" s="4"/>
       <c r="BS14" s="4"/>
@@ -4175,7 +4207,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -4377,7 +4409,9 @@
       <c r="BO15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP15" s="4"/>
+      <c r="BP15" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BQ15" s="4"/>
       <c r="BR15" s="4"/>
       <c r="BS15" s="4"/>
@@ -4434,7 +4468,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -4610,7 +4644,9 @@
       <c r="BM16" s="4"/>
       <c r="BN16" s="4"/>
       <c r="BO16" s="4"/>
-      <c r="BP16" s="4"/>
+      <c r="BP16" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ16" s="4"/>
       <c r="BR16" s="4"/>
       <c r="BS16" s="4"/>
@@ -4667,7 +4703,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -4869,7 +4905,9 @@
       <c r="BO17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP17" s="4"/>
+      <c r="BP17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ17" s="4"/>
       <c r="BR17" s="4"/>
       <c r="BS17" s="4"/>
@@ -4926,7 +4964,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -5128,7 +5166,9 @@
       <c r="BO18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP18" s="4"/>
+      <c r="BP18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ18" s="4"/>
       <c r="BR18" s="4"/>
       <c r="BS18" s="4"/>
@@ -5185,7 +5225,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -5361,7 +5401,9 @@
       <c r="BM19" s="4"/>
       <c r="BN19" s="4"/>
       <c r="BO19" s="4"/>
-      <c r="BP19" s="4"/>
+      <c r="BP19" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ19" s="4"/>
       <c r="BR19" s="4"/>
       <c r="BS19" s="4"/>
@@ -5418,7 +5460,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -5620,7 +5662,9 @@
       <c r="BO20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP20" s="4"/>
+      <c r="BP20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ20" s="4"/>
       <c r="BR20" s="4"/>
       <c r="BS20" s="4"/>
@@ -5677,7 +5721,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -5879,7 +5923,9 @@
       <c r="BO21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP21" s="4"/>
+      <c r="BP21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ21" s="4"/>
       <c r="BR21" s="4"/>
       <c r="BS21" s="4"/>
@@ -5936,7 +5982,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -6138,7 +6184,9 @@
       <c r="BO22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP22" s="4"/>
+      <c r="BP22" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BQ22" s="4"/>
       <c r="BR22" s="4"/>
       <c r="BS22" s="4"/>
@@ -6195,7 +6243,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -6397,7 +6445,9 @@
       <c r="BO23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP23" s="4"/>
+      <c r="BP23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ23" s="4"/>
       <c r="BR23" s="4"/>
       <c r="BS23" s="4"/>
@@ -6454,7 +6504,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -6635,7 +6685,9 @@
       <c r="BO24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP24" s="4"/>
+      <c r="BP24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ24" s="4"/>
       <c r="BR24" s="4"/>
       <c r="BS24" s="4"/>
@@ -6692,7 +6744,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -6894,7 +6946,9 @@
       <c r="BO25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP25" s="4"/>
+      <c r="BP25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ25" s="4"/>
       <c r="BR25" s="4"/>
       <c r="BS25" s="4"/>
@@ -6951,7 +7005,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -7153,7 +7207,9 @@
       <c r="BO26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP26" s="4"/>
+      <c r="BP26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ26" s="4"/>
       <c r="BR26" s="4"/>
       <c r="BS26" s="4"/>
@@ -7210,7 +7266,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -7412,7 +7468,9 @@
       <c r="BO27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP27" s="4"/>
+      <c r="BP27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ27" s="4"/>
       <c r="BR27" s="4"/>
       <c r="BS27" s="4"/>
@@ -7469,7 +7527,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -7671,7 +7729,9 @@
       <c r="BO28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP28" s="4"/>
+      <c r="BP28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ28" s="4"/>
       <c r="BR28" s="4"/>
       <c r="BS28" s="4"/>
@@ -7728,7 +7788,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -7930,7 +7990,9 @@
       <c r="BO29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP29" s="4"/>
+      <c r="BP29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ29" s="4"/>
       <c r="BR29" s="4"/>
       <c r="BS29" s="4"/>
@@ -7987,7 +8049,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -8189,7 +8251,9 @@
       <c r="BO30" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BP30" s="4"/>
+      <c r="BP30" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BQ30" s="4"/>
       <c r="BR30" s="4"/>
       <c r="BS30" s="4"/>
@@ -8246,7 +8310,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -8448,7 +8512,9 @@
       <c r="BO31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BP31" s="4"/>
+      <c r="BP31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BQ31" s="4"/>
       <c r="BR31" s="4"/>
       <c r="BS31" s="4"/>
@@ -8505,7 +8571,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -8707,8 +8773,11 @@
       <c r="BO32" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="BP32" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -8910,8 +8979,11 @@
       <c r="BO33" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="BP33" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="34" spans="1:67" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:68" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -9111,6 +9183,9 @@
         <v>5</v>
       </c>
       <c r="BO34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BP34" s="4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -9119,7 +9194,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BI3:DG4 BB3:BB22 BC3:BC31 BF3:BG31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 BL5:DG12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:DG31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34 BO32:BO34">
+  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BI3:DG3 BB3:BB22 BC3:BC31 BF3:BG31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 BL5:BO12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:BO31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34 BO32:BO34 BI4:BO4 BQ4:DG31 BP4:BP34">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -9152,13 +9227,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -9166,7 +9241,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -9174,7 +9249,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -9182,7 +9257,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -9190,7 +9265,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -9198,7 +9273,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -9206,7 +9281,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -9214,7 +9289,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -9222,7 +9297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -9230,7 +9305,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -9238,7 +9313,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -9246,7 +9321,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -9254,7 +9329,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -9262,7 +9337,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -9270,7 +9345,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -9278,7 +9353,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -9286,7 +9361,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -9294,7 +9369,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -9302,7 +9377,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -9310,7 +9385,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -9318,7 +9393,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -9326,7 +9401,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -9334,7 +9409,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -9342,7 +9417,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -9350,7 +9425,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -9358,7 +9433,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -9366,7 +9441,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -9374,7 +9449,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -9382,7 +9457,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -9390,7 +9465,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -9398,7 +9473,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -9406,7 +9481,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -9414,7 +9489,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20C03C9-7E11-48DD-B1BF-F15661B700B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E857F2-B572-47C0-88B4-49615F6EAD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2174" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2204" uniqueCount="53">
   <si>
     <t>TER</t>
   </si>
@@ -619,36 +619,36 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="39" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.6640625" customWidth="1"/>
-    <col min="42" max="46" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="32" max="39" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.7109375" customWidth="1"/>
+    <col min="42" max="46" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="47" max="47" width="7" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="6.140625" bestFit="1" customWidth="1"/>
     <col min="50" max="50" width="7" bestFit="1" customWidth="1"/>
     <col min="51" max="51" width="7" style="4" bestFit="1" customWidth="1"/>
     <col min="52" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="59" width="7.6640625" customWidth="1"/>
-    <col min="60" max="60" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="61" max="106" width="7.6640625" customWidth="1"/>
+    <col min="55" max="59" width="7.7109375" customWidth="1"/>
+    <col min="60" max="60" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="61" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -870,7 +870,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1102,7 +1102,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1307,7 +1307,9 @@
       <c r="BP3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ3" s="4"/>
+      <c r="BQ3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR3" s="4"/>
       <c r="BS3" s="4"/>
       <c r="BT3" s="4"/>
@@ -1363,7 +1365,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1568,7 +1570,9 @@
       <c r="BP4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ4" s="4"/>
+      <c r="BQ4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR4" s="4"/>
       <c r="BS4" s="4"/>
       <c r="BT4" s="4"/>
@@ -1624,7 +1628,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1829,7 +1833,9 @@
       <c r="BP5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ5" s="4"/>
+      <c r="BQ5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR5" s="4"/>
       <c r="BS5" s="4"/>
       <c r="BT5" s="4"/>
@@ -1885,7 +1891,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -2090,7 +2096,9 @@
       <c r="BP6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ6" s="4"/>
+      <c r="BQ6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR6" s="4"/>
       <c r="BS6" s="4"/>
       <c r="BT6" s="4"/>
@@ -2146,7 +2154,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -2333,7 +2341,9 @@
       <c r="BP7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ7" s="4"/>
+      <c r="BQ7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR7" s="4"/>
       <c r="BS7" s="4"/>
       <c r="BT7" s="4"/>
@@ -2389,7 +2399,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2594,7 +2604,9 @@
       <c r="BP8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ8" s="4"/>
+      <c r="BQ8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR8" s="4"/>
       <c r="BS8" s="4"/>
       <c r="BT8" s="4"/>
@@ -2650,7 +2662,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2855,7 +2867,9 @@
       <c r="BP9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ9" s="4"/>
+      <c r="BQ9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR9" s="4"/>
       <c r="BS9" s="4"/>
       <c r="BT9" s="4"/>
@@ -2911,7 +2925,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -3116,7 +3130,9 @@
       <c r="BP10" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BQ10" s="4"/>
+      <c r="BQ10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR10" s="4"/>
       <c r="BS10" s="4"/>
       <c r="BT10" s="4"/>
@@ -3172,7 +3188,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -3377,7 +3393,9 @@
       <c r="BP11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ11" s="4"/>
+      <c r="BQ11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR11" s="4"/>
       <c r="BS11" s="4"/>
       <c r="BT11" s="4"/>
@@ -3433,7 +3451,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -3638,7 +3656,9 @@
       <c r="BP12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ12" s="4"/>
+      <c r="BQ12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR12" s="4"/>
       <c r="BS12" s="4"/>
       <c r="BT12" s="4"/>
@@ -3694,7 +3714,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -3890,7 +3910,9 @@
       <c r="BP13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ13" s="4"/>
+      <c r="BQ13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR13" s="4"/>
       <c r="BS13" s="4"/>
       <c r="BT13" s="4"/>
@@ -3946,7 +3968,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -4151,7 +4173,9 @@
       <c r="BP14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ14" s="4"/>
+      <c r="BQ14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR14" s="4"/>
       <c r="BS14" s="4"/>
       <c r="BT14" s="4"/>
@@ -4207,7 +4231,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -4412,7 +4436,9 @@
       <c r="BP15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BQ15" s="4"/>
+      <c r="BQ15" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BR15" s="4"/>
       <c r="BS15" s="4"/>
       <c r="BT15" s="4"/>
@@ -4468,7 +4494,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -4703,7 +4729,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -4908,7 +4934,9 @@
       <c r="BP17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ17" s="4"/>
+      <c r="BQ17" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="BR17" s="4"/>
       <c r="BS17" s="4"/>
       <c r="BT17" s="4"/>
@@ -4964,7 +4992,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -5169,7 +5197,9 @@
       <c r="BP18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ18" s="4"/>
+      <c r="BQ18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR18" s="4"/>
       <c r="BS18" s="4"/>
       <c r="BT18" s="4"/>
@@ -5225,7 +5255,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -5460,7 +5490,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -5665,7 +5695,9 @@
       <c r="BP20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ20" s="4"/>
+      <c r="BQ20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR20" s="4"/>
       <c r="BS20" s="4"/>
       <c r="BT20" s="4"/>
@@ -5721,7 +5753,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -5926,7 +5958,9 @@
       <c r="BP21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ21" s="4"/>
+      <c r="BQ21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR21" s="4"/>
       <c r="BS21" s="4"/>
       <c r="BT21" s="4"/>
@@ -5982,7 +6016,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -6187,7 +6221,9 @@
       <c r="BP22" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BQ22" s="4"/>
+      <c r="BQ22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR22" s="4"/>
       <c r="BS22" s="4"/>
       <c r="BT22" s="4"/>
@@ -6243,7 +6279,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -6448,7 +6484,9 @@
       <c r="BP23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ23" s="4"/>
+      <c r="BQ23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR23" s="4"/>
       <c r="BS23" s="4"/>
       <c r="BT23" s="4"/>
@@ -6504,7 +6542,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -6688,7 +6726,9 @@
       <c r="BP24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ24" s="4"/>
+      <c r="BQ24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR24" s="4"/>
       <c r="BS24" s="4"/>
       <c r="BT24" s="4"/>
@@ -6744,7 +6784,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -6949,7 +6989,9 @@
       <c r="BP25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ25" s="4"/>
+      <c r="BQ25" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="BR25" s="4"/>
       <c r="BS25" s="4"/>
       <c r="BT25" s="4"/>
@@ -7005,7 +7047,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -7210,7 +7252,9 @@
       <c r="BP26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ26" s="4"/>
+      <c r="BQ26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR26" s="4"/>
       <c r="BS26" s="4"/>
       <c r="BT26" s="4"/>
@@ -7266,7 +7310,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -7471,7 +7515,9 @@
       <c r="BP27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ27" s="4"/>
+      <c r="BQ27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR27" s="4"/>
       <c r="BS27" s="4"/>
       <c r="BT27" s="4"/>
@@ -7527,7 +7573,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -7732,7 +7778,9 @@
       <c r="BP28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ28" s="4"/>
+      <c r="BQ28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR28" s="4"/>
       <c r="BS28" s="4"/>
       <c r="BT28" s="4"/>
@@ -7788,7 +7836,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -7993,7 +8041,9 @@
       <c r="BP29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ29" s="4"/>
+      <c r="BQ29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR29" s="4"/>
       <c r="BS29" s="4"/>
       <c r="BT29" s="4"/>
@@ -8049,7 +8099,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -8254,7 +8304,9 @@
       <c r="BP30" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BQ30" s="4"/>
+      <c r="BQ30" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BR30" s="4"/>
       <c r="BS30" s="4"/>
       <c r="BT30" s="4"/>
@@ -8310,7 +8362,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -8515,7 +8567,9 @@
       <c r="BP31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BQ31" s="4"/>
+      <c r="BQ31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BR31" s="4"/>
       <c r="BS31" s="4"/>
       <c r="BT31" s="4"/>
@@ -8571,7 +8625,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -8776,8 +8830,11 @@
       <c r="BP32" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="BQ32" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -8982,8 +9039,11 @@
       <c r="BP33" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="BQ33" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="34" spans="1:68" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:69" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -9186,6 +9246,9 @@
         <v>5</v>
       </c>
       <c r="BP34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BQ34" s="4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -9194,7 +9257,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 AV3:AZ4 BI3:DG3 BB3:BB22 BC3:BC31 BF3:BG31 O3:AT34 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 BL5:BO12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:BO31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34 BO32:BO34 BI4:BO4 BQ4:DG31 BP4:BP34">
+  <conditionalFormatting sqref="D3:N3 BI3:DG3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:BG31 O3:AT34 BI4:BO4 D4:I31 K4:M31 BQ4:DG31 J4:J34 N4:N34 BP4:BP34 AZ5:AZ10 BL5:BO12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:BO31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34 BO32:BO34 BQ32:BQ34">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -9227,13 +9290,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -9241,7 +9304,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -9249,7 +9312,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -9257,7 +9320,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -9265,7 +9328,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -9273,7 +9336,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -9281,7 +9344,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -9289,7 +9352,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -9297,7 +9360,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -9305,7 +9368,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -9313,7 +9376,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -9321,7 +9384,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -9329,7 +9392,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -9337,7 +9400,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -9345,7 +9408,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -9353,7 +9416,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -9361,7 +9424,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -9369,7 +9432,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -9377,7 +9440,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -9385,7 +9448,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -9393,7 +9456,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -9401,7 +9464,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -9409,7 +9472,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -9417,7 +9480,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -9425,7 +9488,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -9433,7 +9496,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -9441,7 +9504,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -9449,7 +9512,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -9457,7 +9520,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -9465,7 +9528,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -9473,7 +9536,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -9481,7 +9544,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -9489,7 +9552,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78E857F2-B572-47C0-88B4-49615F6EAD69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396DAC3D-B8E1-4622-B93F-EF8DD2266ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2204" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2304" uniqueCount="54">
   <si>
     <t>TER</t>
   </si>
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t>P/8</t>
+  </si>
+  <si>
+    <t>TECHDAY</t>
   </si>
 </sst>
 </file>
@@ -619,36 +622,41 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="22" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="39" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.7109375" customWidth="1"/>
-    <col min="42" max="46" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="7" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="7" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="7" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="54" width="7" bestFit="1" customWidth="1"/>
-    <col min="55" max="59" width="7.7109375" customWidth="1"/>
-    <col min="60" max="60" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="61" max="106" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="22" width="7" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="39" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="42" max="46" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.77734375" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="57" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="58" max="59" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="61" max="66" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="67" max="69" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="72" max="73" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="74" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -847,12 +855,24 @@
       <c r="BQ1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="BR1" s="3"/>
-      <c r="BS1" s="3"/>
-      <c r="BT1" s="3"/>
-      <c r="BU1" s="3"/>
-      <c r="BV1" s="3"/>
-      <c r="BW1" s="3"/>
+      <c r="BR1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="BS1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BT1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="BU1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="BV1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="BW1" s="3" t="s">
+        <v>1</v>
+      </c>
       <c r="BX1" s="3"/>
       <c r="BY1" s="3"/>
       <c r="BZ1" s="3"/>
@@ -870,7 +890,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1079,20 +1099,28 @@
       <c r="BQ2" s="1">
         <v>46303</v>
       </c>
-      <c r="BR2" s="4"/>
-      <c r="BS2" s="4"/>
-      <c r="BT2" s="4"/>
-      <c r="BU2" s="4"/>
-      <c r="BV2" s="4"/>
-      <c r="BW2" s="4"/>
-      <c r="BX2" s="4"/>
-      <c r="BY2" s="4"/>
-      <c r="BZ2" s="4"/>
-      <c r="CA2" s="4"/>
-      <c r="CB2" s="4"/>
-      <c r="CC2" s="4"/>
-      <c r="CD2" s="4"/>
-      <c r="CE2" s="4"/>
+      <c r="BR2" s="1">
+        <v>46308</v>
+      </c>
+      <c r="BS2" s="1">
+        <v>46310</v>
+      </c>
+      <c r="BT2" s="1">
+        <v>46315</v>
+      </c>
+      <c r="BU2" s="1">
+        <v>46317</v>
+      </c>
+      <c r="BV2" s="1"/>
+      <c r="BW2" s="1"/>
+      <c r="BX2" s="1"/>
+      <c r="BY2" s="1"/>
+      <c r="BZ2" s="1"/>
+      <c r="CA2" s="1"/>
+      <c r="CB2" s="1"/>
+      <c r="CC2" s="1"/>
+      <c r="CD2" s="1"/>
+      <c r="CE2" s="1"/>
       <c r="CF2" s="4"/>
       <c r="CG2" s="4"/>
       <c r="CH2" s="4"/>
@@ -1102,7 +1130,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1310,9 +1338,15 @@
       <c r="BQ3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR3" s="4"/>
-      <c r="BS3" s="4"/>
-      <c r="BT3" s="4"/>
+      <c r="BR3" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU3" s="4"/>
       <c r="BV3" s="4"/>
       <c r="BW3" s="4"/>
@@ -1365,7 +1399,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1573,9 +1607,15 @@
       <c r="BQ4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR4" s="4"/>
-      <c r="BS4" s="4"/>
-      <c r="BT4" s="4"/>
+      <c r="BR4" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU4" s="4"/>
       <c r="BV4" s="4"/>
       <c r="BW4" s="4"/>
@@ -1628,7 +1668,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1836,9 +1876,15 @@
       <c r="BQ5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR5" s="4"/>
-      <c r="BS5" s="4"/>
-      <c r="BT5" s="4"/>
+      <c r="BR5" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU5" s="4"/>
       <c r="BV5" s="4"/>
       <c r="BW5" s="4"/>
@@ -1891,7 +1937,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -2099,9 +2145,15 @@
       <c r="BQ6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR6" s="4"/>
-      <c r="BS6" s="4"/>
-      <c r="BT6" s="4"/>
+      <c r="BR6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS6" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU6" s="4"/>
       <c r="BV6" s="4"/>
       <c r="BW6" s="4"/>
@@ -2154,7 +2206,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -2344,9 +2396,15 @@
       <c r="BQ7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR7" s="4"/>
-      <c r="BS7" s="4"/>
-      <c r="BT7" s="4"/>
+      <c r="BR7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS7" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU7" s="4"/>
       <c r="BV7" s="4"/>
       <c r="BW7" s="4"/>
@@ -2399,7 +2457,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2607,9 +2665,15 @@
       <c r="BQ8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR8" s="4"/>
-      <c r="BS8" s="4"/>
-      <c r="BT8" s="4"/>
+      <c r="BR8" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU8" s="4"/>
       <c r="BV8" s="4"/>
       <c r="BW8" s="4"/>
@@ -2662,7 +2726,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2870,9 +2934,15 @@
       <c r="BQ9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR9" s="4"/>
-      <c r="BS9" s="4"/>
-      <c r="BT9" s="4"/>
+      <c r="BR9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU9" s="4"/>
       <c r="BV9" s="4"/>
       <c r="BW9" s="4"/>
@@ -2925,7 +2995,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -3133,9 +3203,15 @@
       <c r="BQ10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR10" s="4"/>
-      <c r="BS10" s="4"/>
-      <c r="BT10" s="4"/>
+      <c r="BR10" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU10" s="4"/>
       <c r="BV10" s="4"/>
       <c r="BW10" s="4"/>
@@ -3188,7 +3264,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -3396,9 +3472,15 @@
       <c r="BQ11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR11" s="4"/>
-      <c r="BS11" s="4"/>
-      <c r="BT11" s="4"/>
+      <c r="BR11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS11" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU11" s="4"/>
       <c r="BV11" s="4"/>
       <c r="BW11" s="4"/>
@@ -3451,7 +3533,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -3659,9 +3741,15 @@
       <c r="BQ12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR12" s="4"/>
-      <c r="BS12" s="4"/>
-      <c r="BT12" s="4"/>
+      <c r="BR12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS12" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU12" s="4"/>
       <c r="BV12" s="4"/>
       <c r="BW12" s="4"/>
@@ -3714,7 +3802,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -3913,9 +4001,15 @@
       <c r="BQ13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR13" s="4"/>
-      <c r="BS13" s="4"/>
-      <c r="BT13" s="4"/>
+      <c r="BR13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS13" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU13" s="4"/>
       <c r="BV13" s="4"/>
       <c r="BW13" s="4"/>
@@ -3968,7 +4062,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -4176,9 +4270,15 @@
       <c r="BQ14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR14" s="4"/>
-      <c r="BS14" s="4"/>
-      <c r="BT14" s="4"/>
+      <c r="BR14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS14" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU14" s="4"/>
       <c r="BV14" s="4"/>
       <c r="BW14" s="4"/>
@@ -4231,7 +4331,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -4439,9 +4539,15 @@
       <c r="BQ15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BR15" s="4"/>
-      <c r="BS15" s="4"/>
-      <c r="BT15" s="4"/>
+      <c r="BR15" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS15" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU15" s="4"/>
       <c r="BV15" s="4"/>
       <c r="BW15" s="4"/>
@@ -4494,7 +4600,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -4674,8 +4780,12 @@
         <v>5</v>
       </c>
       <c r="BQ16" s="4"/>
-      <c r="BR16" s="4"/>
-      <c r="BS16" s="4"/>
+      <c r="BR16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS16" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="BT16" s="4"/>
       <c r="BU16" s="4"/>
       <c r="BV16" s="4"/>
@@ -4729,7 +4839,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -4937,9 +5047,15 @@
       <c r="BQ17" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="BR17" s="4"/>
-      <c r="BS17" s="4"/>
-      <c r="BT17" s="4"/>
+      <c r="BR17" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS17" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU17" s="4"/>
       <c r="BV17" s="4"/>
       <c r="BW17" s="4"/>
@@ -4992,7 +5108,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -5200,9 +5316,15 @@
       <c r="BQ18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR18" s="4"/>
-      <c r="BS18" s="4"/>
-      <c r="BT18" s="4"/>
+      <c r="BR18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU18" s="4"/>
       <c r="BV18" s="4"/>
       <c r="BW18" s="4"/>
@@ -5255,7 +5377,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -5435,8 +5557,12 @@
         <v>5</v>
       </c>
       <c r="BQ19" s="4"/>
-      <c r="BR19" s="4"/>
-      <c r="BS19" s="4"/>
+      <c r="BR19" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS19" s="4" t="s">
+        <v>53</v>
+      </c>
       <c r="BT19" s="4"/>
       <c r="BU19" s="4"/>
       <c r="BV19" s="4"/>
@@ -5490,7 +5616,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -5698,9 +5824,15 @@
       <c r="BQ20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR20" s="4"/>
-      <c r="BS20" s="4"/>
-      <c r="BT20" s="4"/>
+      <c r="BR20" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS20" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU20" s="4"/>
       <c r="BV20" s="4"/>
       <c r="BW20" s="4"/>
@@ -5753,7 +5885,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -5961,9 +6093,15 @@
       <c r="BQ21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR21" s="4"/>
-      <c r="BS21" s="4"/>
-      <c r="BT21" s="4"/>
+      <c r="BR21" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS21" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU21" s="4"/>
       <c r="BV21" s="4"/>
       <c r="BW21" s="4"/>
@@ -6016,7 +6154,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -6224,9 +6362,15 @@
       <c r="BQ22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR22" s="4"/>
-      <c r="BS22" s="4"/>
-      <c r="BT22" s="4"/>
+      <c r="BR22" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS22" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU22" s="4"/>
       <c r="BV22" s="4"/>
       <c r="BW22" s="4"/>
@@ -6279,7 +6423,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -6487,9 +6631,15 @@
       <c r="BQ23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR23" s="4"/>
-      <c r="BS23" s="4"/>
-      <c r="BT23" s="4"/>
+      <c r="BR23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS23" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU23" s="4"/>
       <c r="BV23" s="4"/>
       <c r="BW23" s="4"/>
@@ -6542,7 +6692,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -6729,9 +6879,15 @@
       <c r="BQ24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR24" s="4"/>
-      <c r="BS24" s="4"/>
-      <c r="BT24" s="4"/>
+      <c r="BR24" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS24" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU24" s="4"/>
       <c r="BV24" s="4"/>
       <c r="BW24" s="4"/>
@@ -6784,7 +6940,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -6992,9 +7148,15 @@
       <c r="BQ25" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="BR25" s="4"/>
-      <c r="BS25" s="4"/>
-      <c r="BT25" s="4"/>
+      <c r="BR25" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS25" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU25" s="4"/>
       <c r="BV25" s="4"/>
       <c r="BW25" s="4"/>
@@ -7047,7 +7209,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -7255,9 +7417,15 @@
       <c r="BQ26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR26" s="4"/>
-      <c r="BS26" s="4"/>
-      <c r="BT26" s="4"/>
+      <c r="BR26" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS26" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU26" s="4"/>
       <c r="BV26" s="4"/>
       <c r="BW26" s="4"/>
@@ -7310,7 +7478,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -7518,9 +7686,15 @@
       <c r="BQ27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR27" s="4"/>
-      <c r="BS27" s="4"/>
-      <c r="BT27" s="4"/>
+      <c r="BR27" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS27" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU27" s="4"/>
       <c r="BV27" s="4"/>
       <c r="BW27" s="4"/>
@@ -7573,7 +7747,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -7781,9 +7955,15 @@
       <c r="BQ28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR28" s="4"/>
-      <c r="BS28" s="4"/>
-      <c r="BT28" s="4"/>
+      <c r="BR28" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS28" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU28" s="4"/>
       <c r="BV28" s="4"/>
       <c r="BW28" s="4"/>
@@ -7836,7 +8016,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -8044,9 +8224,15 @@
       <c r="BQ29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR29" s="4"/>
-      <c r="BS29" s="4"/>
-      <c r="BT29" s="4"/>
+      <c r="BR29" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS29" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT29" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BU29" s="4"/>
       <c r="BV29" s="4"/>
       <c r="BW29" s="4"/>
@@ -8099,7 +8285,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -8307,9 +8493,15 @@
       <c r="BQ30" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BR30" s="4"/>
-      <c r="BS30" s="4"/>
-      <c r="BT30" s="4"/>
+      <c r="BR30" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS30" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU30" s="4"/>
       <c r="BV30" s="4"/>
       <c r="BW30" s="4"/>
@@ -8362,7 +8554,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -8570,9 +8762,15 @@
       <c r="BQ31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BR31" s="4"/>
-      <c r="BS31" s="4"/>
-      <c r="BT31" s="4"/>
+      <c r="BR31" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS31" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BU31" s="4"/>
       <c r="BV31" s="4"/>
       <c r="BW31" s="4"/>
@@ -8625,7 +8823,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -8833,8 +9031,17 @@
       <c r="BQ32" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="BR32" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS32" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT32" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -9042,8 +9249,17 @@
       <c r="BQ33" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="BR33" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS33" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT33" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="34" spans="1:69" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:72" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -9249,6 +9465,15 @@
         <v>5</v>
       </c>
       <c r="BQ34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BR34" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="BS34" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="BT34" s="4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -9257,7 +9482,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BI3:DG3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:BG31 O3:AT34 BI4:BO4 D4:I31 K4:M31 BQ4:DG31 J4:J34 N4:N34 BP4:BP34 AZ5:AZ10 BL5:BO12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:BO31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34 BO32:BO34 BQ32:BQ34">
+  <conditionalFormatting sqref="D3:N3 BI3:DG3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:BG31 O3:AT34 BI4:BO4 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 BL5:BO12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:BO31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34 BO32:BO34 BT32:BT34 BT4:DG31 BP4:BS34">
     <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -9290,13 +9515,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -9304,7 +9529,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -9312,7 +9537,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -9320,7 +9545,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -9328,7 +9553,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -9336,7 +9561,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -9344,7 +9569,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -9352,7 +9577,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -9360,7 +9585,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -9368,7 +9593,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -9376,7 +9601,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -9384,7 +9609,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -9392,7 +9617,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -9400,7 +9625,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -9408,7 +9633,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -9416,7 +9641,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -9424,7 +9649,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -9432,7 +9657,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -9440,7 +9665,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -9448,7 +9673,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -9456,7 +9681,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -9464,7 +9689,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -9472,7 +9697,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -9480,7 +9705,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -9488,7 +9713,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -9496,7 +9721,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -9504,7 +9729,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -9512,7 +9737,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -9520,7 +9745,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -9528,7 +9753,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -9536,7 +9761,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -9544,7 +9769,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -9552,7 +9777,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{396DAC3D-B8E1-4622-B93F-EF8DD2266ECD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2806E249-E3F0-4A58-BC86-23334980A246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2304" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2336" uniqueCount="54">
   <si>
     <t>TER</t>
   </si>
@@ -205,7 +205,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,6 +246,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -274,7 +281,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -289,12 +296,33 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="7">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -622,41 +650,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="16" width="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="22" width="7" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="39" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="46" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="57" width="6.77734375" bestFit="1" customWidth="1"/>
-    <col min="58" max="59" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="61" max="66" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="67" max="69" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="8.21875" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="72" max="73" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="74" max="106" width="7.6640625" customWidth="1"/>
+    <col min="23" max="27" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="42" max="46" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="57" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="58" max="59" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="61" max="66" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="67" max="69" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="72" max="73" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="74" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -890,7 +917,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1130,7 +1157,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1347,7 +1374,9 @@
       <c r="BT3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU3" s="4"/>
+      <c r="BU3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV3" s="4"/>
       <c r="BW3" s="4"/>
       <c r="BX3" s="4"/>
@@ -1399,7 +1428,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1616,7 +1645,9 @@
       <c r="BT4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU4" s="4"/>
+      <c r="BU4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV4" s="4"/>
       <c r="BW4" s="4"/>
       <c r="BX4" s="4"/>
@@ -1668,7 +1699,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1885,9 +1916,11 @@
       <c r="BT5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU5" s="4"/>
+      <c r="BU5" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BV5" s="4"/>
-      <c r="BW5" s="4"/>
+      <c r="BW5" s="10"/>
       <c r="BX5" s="4"/>
       <c r="BY5" s="4"/>
       <c r="BZ5" s="4"/>
@@ -1937,7 +1970,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -2154,9 +2187,11 @@
       <c r="BT6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU6" s="4"/>
+      <c r="BU6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV6" s="4"/>
-      <c r="BW6" s="4"/>
+      <c r="BW6" s="10"/>
       <c r="BX6" s="4"/>
       <c r="BY6" s="4"/>
       <c r="BZ6" s="4"/>
@@ -2206,7 +2241,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -2405,7 +2440,9 @@
       <c r="BT7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU7" s="4"/>
+      <c r="BU7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV7" s="4"/>
       <c r="BW7" s="4"/>
       <c r="BX7" s="4"/>
@@ -2457,7 +2494,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2674,7 +2711,9 @@
       <c r="BT8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU8" s="4"/>
+      <c r="BU8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV8" s="4"/>
       <c r="BW8" s="4"/>
       <c r="BX8" s="4"/>
@@ -2726,7 +2765,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2943,7 +2982,9 @@
       <c r="BT9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU9" s="4"/>
+      <c r="BU9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV9" s="4"/>
       <c r="BW9" s="4"/>
       <c r="BX9" s="4"/>
@@ -2995,7 +3036,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -3212,7 +3253,9 @@
       <c r="BT10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU10" s="4"/>
+      <c r="BU10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV10" s="4"/>
       <c r="BW10" s="4"/>
       <c r="BX10" s="4"/>
@@ -3264,7 +3307,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -3481,7 +3524,9 @@
       <c r="BT11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU11" s="4"/>
+      <c r="BU11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV11" s="4"/>
       <c r="BW11" s="4"/>
       <c r="BX11" s="4"/>
@@ -3533,7 +3578,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -3750,7 +3795,9 @@
       <c r="BT12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU12" s="4"/>
+      <c r="BU12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV12" s="4"/>
       <c r="BW12" s="4"/>
       <c r="BX12" s="4"/>
@@ -3802,7 +3849,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -4010,7 +4057,9 @@
       <c r="BT13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU13" s="4"/>
+      <c r="BU13" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BV13" s="4"/>
       <c r="BW13" s="4"/>
       <c r="BX13" s="4"/>
@@ -4062,7 +4111,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -4279,7 +4328,9 @@
       <c r="BT14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU14" s="4"/>
+      <c r="BU14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV14" s="4"/>
       <c r="BW14" s="4"/>
       <c r="BX14" s="4"/>
@@ -4331,7 +4382,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -4548,7 +4599,9 @@
       <c r="BT15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU15" s="4"/>
+      <c r="BU15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV15" s="4"/>
       <c r="BW15" s="4"/>
       <c r="BX15" s="4"/>
@@ -4600,7 +4653,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -4787,7 +4840,9 @@
         <v>53</v>
       </c>
       <c r="BT16" s="4"/>
-      <c r="BU16" s="4"/>
+      <c r="BU16" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV16" s="4"/>
       <c r="BW16" s="4"/>
       <c r="BX16" s="4"/>
@@ -4839,7 +4894,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -5056,7 +5111,9 @@
       <c r="BT17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU17" s="4"/>
+      <c r="BU17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV17" s="4"/>
       <c r="BW17" s="4"/>
       <c r="BX17" s="4"/>
@@ -5108,7 +5165,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -5325,7 +5382,9 @@
       <c r="BT18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU18" s="4"/>
+      <c r="BU18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV18" s="4"/>
       <c r="BW18" s="4"/>
       <c r="BX18" s="4"/>
@@ -5377,7 +5436,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -5564,7 +5623,9 @@
         <v>53</v>
       </c>
       <c r="BT19" s="4"/>
-      <c r="BU19" s="4"/>
+      <c r="BU19" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV19" s="4"/>
       <c r="BW19" s="4"/>
       <c r="BX19" s="4"/>
@@ -5616,7 +5677,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -5833,7 +5894,9 @@
       <c r="BT20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU20" s="4"/>
+      <c r="BU20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV20" s="4"/>
       <c r="BW20" s="4"/>
       <c r="BX20" s="4"/>
@@ -5885,7 +5948,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -6102,7 +6165,9 @@
       <c r="BT21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU21" s="4"/>
+      <c r="BU21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV21" s="4"/>
       <c r="BW21" s="4"/>
       <c r="BX21" s="4"/>
@@ -6154,7 +6219,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -6371,7 +6436,9 @@
       <c r="BT22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU22" s="4"/>
+      <c r="BU22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV22" s="4"/>
       <c r="BW22" s="4"/>
       <c r="BX22" s="4"/>
@@ -6423,7 +6490,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -6640,7 +6707,9 @@
       <c r="BT23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU23" s="4"/>
+      <c r="BU23" s="4" t="s">
+        <v>7</v>
+      </c>
       <c r="BV23" s="4"/>
       <c r="BW23" s="4"/>
       <c r="BX23" s="4"/>
@@ -6692,7 +6761,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -6888,7 +6957,9 @@
       <c r="BT24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU24" s="4"/>
+      <c r="BU24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV24" s="4"/>
       <c r="BW24" s="4"/>
       <c r="BX24" s="4"/>
@@ -6940,7 +7011,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -7157,7 +7228,9 @@
       <c r="BT25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU25" s="4"/>
+      <c r="BU25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV25" s="4"/>
       <c r="BW25" s="4"/>
       <c r="BX25" s="4"/>
@@ -7209,7 +7282,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -7426,7 +7499,9 @@
       <c r="BT26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU26" s="4"/>
+      <c r="BU26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV26" s="4"/>
       <c r="BW26" s="4"/>
       <c r="BX26" s="4"/>
@@ -7478,7 +7553,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -7695,7 +7770,9 @@
       <c r="BT27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU27" s="4"/>
+      <c r="BU27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV27" s="4"/>
       <c r="BW27" s="4"/>
       <c r="BX27" s="4"/>
@@ -7747,7 +7824,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -7964,7 +8041,9 @@
       <c r="BT28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU28" s="4"/>
+      <c r="BU28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV28" s="4"/>
       <c r="BW28" s="4"/>
       <c r="BX28" s="4"/>
@@ -8016,7 +8095,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -8233,7 +8312,9 @@
       <c r="BT29" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BU29" s="4"/>
+      <c r="BU29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV29" s="4"/>
       <c r="BW29" s="4"/>
       <c r="BX29" s="4"/>
@@ -8285,7 +8366,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -8502,7 +8583,9 @@
       <c r="BT30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU30" s="4"/>
+      <c r="BU30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV30" s="4"/>
       <c r="BW30" s="4"/>
       <c r="BX30" s="4"/>
@@ -8554,7 +8637,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -8771,7 +8854,9 @@
       <c r="BT31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BU31" s="4"/>
+      <c r="BU31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BV31" s="4"/>
       <c r="BW31" s="4"/>
       <c r="BX31" s="4"/>
@@ -8823,7 +8908,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -9040,8 +9125,11 @@
       <c r="BT32" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="BU32" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -9258,8 +9346,11 @@
       <c r="BT33" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="BU33" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="34" spans="1:72" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -9475,6 +9566,9 @@
       </c>
       <c r="BT34" s="4" t="s">
         <v>5</v>
+      </c>
+      <c r="BU34" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -9482,27 +9576,32 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BI3:DG3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:BG31 O3:AT34 BI4:BO4 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 BL5:BO12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:BO31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34 BO32:BO34 BT32:BT34 BT4:DG31 BP4:BS34">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+  <conditionalFormatting sqref="D3:N3 BI3:BT3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:BG31 O3:AT34 BI4:BO4 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 BL5:BO12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:BO31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34 BO32:BO34 BP4:BT34 BV3:DG31">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA23">
-    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BA23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB3:BC34">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BB3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB34:BC34">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI32">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"F"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="BU3:BU34">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -9515,13 +9614,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -9529,7 +9628,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -9537,7 +9636,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -9545,7 +9644,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -9553,7 +9652,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -9561,7 +9660,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -9569,7 +9668,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -9577,7 +9676,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -9585,7 +9684,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -9593,7 +9692,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -9601,7 +9700,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -9609,7 +9708,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -9617,7 +9716,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -9625,7 +9724,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -9633,7 +9732,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -9641,7 +9740,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -9649,7 +9748,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -9657,7 +9756,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -9665,7 +9764,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -9673,7 +9772,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -9681,7 +9780,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -9689,7 +9788,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -9697,7 +9796,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -9705,7 +9804,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -9713,7 +9812,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -9721,7 +9820,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -9729,7 +9828,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -9737,7 +9836,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -9745,7 +9844,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -9753,7 +9852,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -9761,7 +9860,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -9769,7 +9868,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -9777,7 +9876,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1089986\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2806E249-E3F0-4A58-BC86-23334980A246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771C2FBA-C262-48FE-AD95-CF0B0B104F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -302,17 +302,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentagem" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="6">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -6708,7 +6698,7 @@
         <v>5</v>
       </c>
       <c r="BU23" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="BV23" s="4"/>
       <c r="BW23" s="4"/>
@@ -9576,28 +9566,28 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BI3:BT3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:BG31 O3:AT34 BI4:BO4 D4:I31 K4:M31 J4:J34 N4:N34 AZ5:AZ10 BL5:BO12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:BO31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34 BO32:BO34 BP4:BT34 BV3:DG31">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+  <conditionalFormatting sqref="D3:N3 BI3:BT3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:BG31 BV3:DG31 O3:AT34 BI4:BO4 D4:I31 K4:M31 J4:J34 N4:N34 BP4:BT34 AZ5:AZ10 BL5:BO12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:BO31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34 BO32:BO34">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BA23">
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BA23)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB3:BC34">
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="F">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="F">
       <formula>NOT(ISERROR(SEARCH("F",BB3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BB34:BC34">
-    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="BI32">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{771C2FBA-C262-48FE-AD95-CF0B0B104F29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0A56B4-E3A7-4C6D-B92E-B6AB79AE5CEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2336" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2366" uniqueCount="54">
   <si>
     <t>TER</t>
   </si>
@@ -640,40 +640,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="16" width="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="22" width="7" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="32" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="42" max="46" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="5.7109375" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.7109375" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="57" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="58" max="59" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="61" max="66" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="67" max="69" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="72" max="73" width="6.5703125" bestFit="1" customWidth="1"/>
-    <col min="74" max="106" width="7.7109375" customWidth="1"/>
+    <col min="23" max="27" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="39" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="42" max="46" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="57" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="58" max="59" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="61" max="66" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="67" max="69" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="72" max="73" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="74" max="106" width="7.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -907,7 +907,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1128,8 +1128,12 @@
       <c r="BU2" s="1">
         <v>46317</v>
       </c>
-      <c r="BV2" s="1"/>
-      <c r="BW2" s="1"/>
+      <c r="BV2" s="1">
+        <v>46322</v>
+      </c>
+      <c r="BW2" s="1">
+        <v>46324</v>
+      </c>
       <c r="BX2" s="1"/>
       <c r="BY2" s="1"/>
       <c r="BZ2" s="1"/>
@@ -1147,7 +1151,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1367,7 +1371,9 @@
       <c r="BU3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV3" s="4"/>
+      <c r="BV3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW3" s="4"/>
       <c r="BX3" s="4"/>
       <c r="BY3" s="4"/>
@@ -1418,7 +1424,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1638,7 +1644,9 @@
       <c r="BU4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV4" s="4"/>
+      <c r="BV4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW4" s="4"/>
       <c r="BX4" s="4"/>
       <c r="BY4" s="4"/>
@@ -1689,7 +1697,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1909,7 +1917,9 @@
       <c r="BU5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BV5" s="4"/>
+      <c r="BV5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW5" s="10"/>
       <c r="BX5" s="4"/>
       <c r="BY5" s="4"/>
@@ -1960,7 +1970,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -2180,7 +2190,9 @@
       <c r="BU6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV6" s="4"/>
+      <c r="BV6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW6" s="10"/>
       <c r="BX6" s="4"/>
       <c r="BY6" s="4"/>
@@ -2231,7 +2243,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -2433,7 +2445,9 @@
       <c r="BU7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV7" s="4"/>
+      <c r="BV7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW7" s="4"/>
       <c r="BX7" s="4"/>
       <c r="BY7" s="4"/>
@@ -2484,7 +2498,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2704,7 +2718,9 @@
       <c r="BU8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV8" s="4"/>
+      <c r="BV8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW8" s="4"/>
       <c r="BX8" s="4"/>
       <c r="BY8" s="4"/>
@@ -2755,7 +2771,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2975,7 +2991,9 @@
       <c r="BU9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV9" s="4"/>
+      <c r="BV9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW9" s="4"/>
       <c r="BX9" s="4"/>
       <c r="BY9" s="4"/>
@@ -3026,7 +3044,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -3246,7 +3264,9 @@
       <c r="BU10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV10" s="4"/>
+      <c r="BV10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW10" s="4"/>
       <c r="BX10" s="4"/>
       <c r="BY10" s="4"/>
@@ -3297,7 +3317,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -3517,7 +3537,9 @@
       <c r="BU11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV11" s="4"/>
+      <c r="BV11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW11" s="4"/>
       <c r="BX11" s="4"/>
       <c r="BY11" s="4"/>
@@ -3568,7 +3590,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -3788,7 +3810,9 @@
       <c r="BU12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV12" s="4"/>
+      <c r="BV12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW12" s="4"/>
       <c r="BX12" s="4"/>
       <c r="BY12" s="4"/>
@@ -3839,7 +3863,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -4050,7 +4074,9 @@
       <c r="BU13" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="BV13" s="4"/>
+      <c r="BV13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW13" s="4"/>
       <c r="BX13" s="4"/>
       <c r="BY13" s="4"/>
@@ -4101,7 +4127,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -4321,7 +4347,9 @@
       <c r="BU14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV14" s="4"/>
+      <c r="BV14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW14" s="4"/>
       <c r="BX14" s="4"/>
       <c r="BY14" s="4"/>
@@ -4372,7 +4400,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -4592,7 +4620,9 @@
       <c r="BU15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV15" s="4"/>
+      <c r="BV15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW15" s="4"/>
       <c r="BX15" s="4"/>
       <c r="BY15" s="4"/>
@@ -4643,7 +4673,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -4884,7 +4914,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -5104,7 +5134,9 @@
       <c r="BU17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV17" s="4"/>
+      <c r="BV17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW17" s="4"/>
       <c r="BX17" s="4"/>
       <c r="BY17" s="4"/>
@@ -5155,7 +5187,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -5375,7 +5407,9 @@
       <c r="BU18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV18" s="4"/>
+      <c r="BV18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW18" s="4"/>
       <c r="BX18" s="4"/>
       <c r="BY18" s="4"/>
@@ -5426,7 +5460,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -5667,7 +5701,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -5887,7 +5921,9 @@
       <c r="BU20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV20" s="4"/>
+      <c r="BV20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW20" s="4"/>
       <c r="BX20" s="4"/>
       <c r="BY20" s="4"/>
@@ -5938,7 +5974,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -6158,7 +6194,9 @@
       <c r="BU21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV21" s="4"/>
+      <c r="BV21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW21" s="4"/>
       <c r="BX21" s="4"/>
       <c r="BY21" s="4"/>
@@ -6209,7 +6247,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -6429,7 +6467,9 @@
       <c r="BU22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV22" s="4"/>
+      <c r="BV22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW22" s="4"/>
       <c r="BX22" s="4"/>
       <c r="BY22" s="4"/>
@@ -6480,7 +6520,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -6700,7 +6740,9 @@
       <c r="BU23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV23" s="4"/>
+      <c r="BV23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW23" s="4"/>
       <c r="BX23" s="4"/>
       <c r="BY23" s="4"/>
@@ -6751,7 +6793,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -6950,7 +6992,9 @@
       <c r="BU24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV24" s="4"/>
+      <c r="BV24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW24" s="4"/>
       <c r="BX24" s="4"/>
       <c r="BY24" s="4"/>
@@ -7001,7 +7045,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -7221,7 +7265,9 @@
       <c r="BU25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV25" s="4"/>
+      <c r="BV25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW25" s="4"/>
       <c r="BX25" s="4"/>
       <c r="BY25" s="4"/>
@@ -7272,7 +7318,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -7492,7 +7538,9 @@
       <c r="BU26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV26" s="4"/>
+      <c r="BV26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW26" s="4"/>
       <c r="BX26" s="4"/>
       <c r="BY26" s="4"/>
@@ -7543,7 +7591,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -7763,7 +7811,9 @@
       <c r="BU27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV27" s="4"/>
+      <c r="BV27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW27" s="4"/>
       <c r="BX27" s="4"/>
       <c r="BY27" s="4"/>
@@ -7814,7 +7864,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -8034,7 +8084,9 @@
       <c r="BU28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV28" s="4"/>
+      <c r="BV28" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW28" s="4"/>
       <c r="BX28" s="4"/>
       <c r="BY28" s="4"/>
@@ -8085,7 +8137,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -8305,7 +8357,9 @@
       <c r="BU29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV29" s="4"/>
+      <c r="BV29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW29" s="4"/>
       <c r="BX29" s="4"/>
       <c r="BY29" s="4"/>
@@ -8356,7 +8410,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -8576,7 +8630,9 @@
       <c r="BU30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV30" s="4"/>
+      <c r="BV30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW30" s="4"/>
       <c r="BX30" s="4"/>
       <c r="BY30" s="4"/>
@@ -8627,7 +8683,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -8847,7 +8903,9 @@
       <c r="BU31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BV31" s="4"/>
+      <c r="BV31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BW31" s="4"/>
       <c r="BX31" s="4"/>
       <c r="BY31" s="4"/>
@@ -8898,7 +8956,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -9118,8 +9176,11 @@
       <c r="BU32" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="BV32" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -9339,8 +9400,11 @@
       <c r="BU33" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="BV33" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="34" spans="1:73" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:74" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -9559,6 +9623,9 @@
       </c>
       <c r="BU34" s="4" t="s">
         <v>7</v>
+      </c>
+      <c r="BV34" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -9566,7 +9633,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BI3:BT3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:BG31 BV3:DG31 O3:AT34 BI4:BO4 D4:I31 K4:M31 J4:J34 N4:N34 BP4:BT34 AZ5:AZ10 BL5:BO12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:BO31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34 BO32:BO34">
+  <conditionalFormatting sqref="D3:N3 BI3:BT3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:BG31 BV3:DG31 O3:AT34 BI4:BO4 D4:I31 K4:M31 J4:J34 N4:N34 BP4:BT34 AZ5:AZ10 BL5:BO12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:BO31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34 BO32:BO34 BV32:BV34">
     <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -9604,13 +9671,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -9618,7 +9685,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -9626,7 +9693,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -9634,7 +9701,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -9642,7 +9709,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -9650,7 +9717,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -9658,7 +9725,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -9666,7 +9733,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -9674,7 +9741,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -9682,7 +9749,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -9690,7 +9757,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -9698,7 +9765,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -9706,7 +9773,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -9714,7 +9781,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -9722,7 +9789,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -9730,7 +9797,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -9738,7 +9805,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -9746,7 +9813,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -9754,7 +9821,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -9762,7 +9829,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -9770,7 +9837,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -9778,7 +9845,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -9786,7 +9853,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -9794,7 +9861,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -9802,7 +9869,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -9810,7 +9877,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -9818,7 +9885,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -9826,7 +9893,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -9834,7 +9901,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -9842,7 +9909,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -9850,7 +9917,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -9858,7 +9925,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -9866,7 +9933,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>26132234</v>
       </c>

--- a/ds/turmas/1DES_B/frequencia-2-B.xlsx
+++ b/ds/turmas/1DES_B/frequencia-2-B.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENAI\Desktop\senai2026\ds\turmas\1DES_B\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2026\ds\turmas\1DES_B\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC0A56B4-E3A7-4C6D-B92E-B6AB79AE5CEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D697C64B-16E2-4805-A79A-839B7C95A7BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="chamada" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2366" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2396" uniqueCount="54">
   <si>
     <t>TER</t>
   </si>
@@ -205,7 +205,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,13 +246,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -281,7 +274,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="16" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -296,7 +289,6 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -640,40 +632,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:DS34"/>
-  <sheetFormatPr defaultColWidth="6.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="9" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="14" max="16" width="7" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="18" max="22" width="7" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="32" max="39" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="42" max="46" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="48" max="49" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="6.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="52" max="57" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="58" max="59" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="61" max="66" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="67" max="69" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="72" max="73" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="74" max="106" width="7.6640625" customWidth="1"/>
+    <col min="23" max="27" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="32" max="39" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="42" max="46" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="48" max="49" width="5.7109375" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="6.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="52" max="57" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="58" max="59" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="61" max="66" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="67" max="69" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="72" max="73" width="6.5703125" bestFit="1" customWidth="1"/>
+    <col min="74" max="106" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:123" x14ac:dyDescent="0.25">
       <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
@@ -907,7 +899,7 @@
       <c r="CL1" s="3"/>
       <c r="CM1" s="3"/>
     </row>
-    <row r="2" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -1151,7 +1143,7 @@
       <c r="CL2" s="4"/>
       <c r="CM2" s="4"/>
     </row>
-    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132174</v>
       </c>
@@ -1374,7 +1366,9 @@
       <c r="BV3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW3" s="4"/>
+      <c r="BW3" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX3" s="4"/>
       <c r="BY3" s="4"/>
       <c r="BZ3" s="4"/>
@@ -1424,7 +1418,7 @@
       <c r="DR3" s="4"/>
       <c r="DS3" s="4"/>
     </row>
-    <row r="4" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132207</v>
       </c>
@@ -1647,7 +1641,9 @@
       <c r="BV4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW4" s="4"/>
+      <c r="BW4" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX4" s="4"/>
       <c r="BY4" s="4"/>
       <c r="BZ4" s="4"/>
@@ -1697,7 +1693,7 @@
       <c r="DR4" s="4"/>
       <c r="DS4" s="4"/>
     </row>
-    <row r="5" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132186</v>
       </c>
@@ -1920,7 +1916,9 @@
       <c r="BV5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW5" s="10"/>
+      <c r="BW5" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX5" s="4"/>
       <c r="BY5" s="4"/>
       <c r="BZ5" s="4"/>
@@ -1970,7 +1968,7 @@
       <c r="DR5" s="4"/>
       <c r="DS5" s="4"/>
     </row>
-    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:123" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26132259</v>
       </c>
@@ -2193,7 +2191,9 @@
       <c r="BV6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW6" s="10"/>
+      <c r="BW6" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX6" s="4"/>
       <c r="BY6" s="4"/>
       <c r="BZ6" s="4"/>
@@ -2243,7 +2243,7 @@
       <c r="DR6" s="4"/>
       <c r="DS6" s="4"/>
     </row>
-    <row r="7" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26133017</v>
       </c>
@@ -2448,7 +2448,9 @@
       <c r="BV7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW7" s="4"/>
+      <c r="BW7" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX7" s="4"/>
       <c r="BY7" s="4"/>
       <c r="BZ7" s="4"/>
@@ -2498,7 +2500,7 @@
       <c r="DR7" s="4"/>
       <c r="DS7" s="4"/>
     </row>
-    <row r="8" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132209</v>
       </c>
@@ -2721,7 +2723,9 @@
       <c r="BV8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW8" s="4"/>
+      <c r="BW8" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX8" s="4"/>
       <c r="BY8" s="4"/>
       <c r="BZ8" s="4"/>
@@ -2771,7 +2775,7 @@
       <c r="DR8" s="4"/>
       <c r="DS8" s="4"/>
     </row>
-    <row r="9" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132211</v>
       </c>
@@ -2994,7 +2998,9 @@
       <c r="BV9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW9" s="4"/>
+      <c r="BW9" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX9" s="4"/>
       <c r="BY9" s="4"/>
       <c r="BZ9" s="4"/>
@@ -3044,7 +3050,7 @@
       <c r="DR9" s="4"/>
       <c r="DS9" s="4"/>
     </row>
-    <row r="10" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132215</v>
       </c>
@@ -3267,7 +3273,9 @@
       <c r="BV10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW10" s="4"/>
+      <c r="BW10" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX10" s="4"/>
       <c r="BY10" s="4"/>
       <c r="BZ10" s="4"/>
@@ -3317,7 +3325,7 @@
       <c r="DR10" s="4"/>
       <c r="DS10" s="4"/>
     </row>
-    <row r="11" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132213</v>
       </c>
@@ -3540,7 +3548,9 @@
       <c r="BV11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW11" s="4"/>
+      <c r="BW11" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX11" s="4"/>
       <c r="BY11" s="4"/>
       <c r="BZ11" s="4"/>
@@ -3590,7 +3600,7 @@
       <c r="DR11" s="4"/>
       <c r="DS11" s="4"/>
     </row>
-    <row r="12" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26132261</v>
       </c>
@@ -3813,7 +3823,9 @@
       <c r="BV12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW12" s="4"/>
+      <c r="BW12" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX12" s="4"/>
       <c r="BY12" s="4"/>
       <c r="BZ12" s="4"/>
@@ -3863,7 +3875,7 @@
       <c r="DR12" s="4"/>
       <c r="DS12" s="4"/>
     </row>
-    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:123" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26133027</v>
       </c>
@@ -4077,7 +4089,9 @@
       <c r="BV13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW13" s="4"/>
+      <c r="BW13" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX13" s="4"/>
       <c r="BY13" s="4"/>
       <c r="BZ13" s="4"/>
@@ -4127,7 +4141,7 @@
       <c r="DR13" s="4"/>
       <c r="DS13" s="4"/>
     </row>
-    <row r="14" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132176</v>
       </c>
@@ -4350,7 +4364,9 @@
       <c r="BV14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW14" s="4"/>
+      <c r="BW14" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX14" s="4"/>
       <c r="BY14" s="4"/>
       <c r="BZ14" s="4"/>
@@ -4400,7 +4416,7 @@
       <c r="DR14" s="4"/>
       <c r="DS14" s="4"/>
     </row>
-    <row r="15" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132254</v>
       </c>
@@ -4623,7 +4639,9 @@
       <c r="BV15" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW15" s="4"/>
+      <c r="BW15" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX15" s="4"/>
       <c r="BY15" s="4"/>
       <c r="BZ15" s="4"/>
@@ -4673,7 +4691,7 @@
       <c r="DR15" s="4"/>
       <c r="DS15" s="4"/>
     </row>
-    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132326</v>
       </c>
@@ -4914,7 +4932,7 @@
       <c r="DR16" s="4"/>
       <c r="DS16" s="4"/>
     </row>
-    <row r="17" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132195</v>
       </c>
@@ -5137,7 +5155,9 @@
       <c r="BV17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW17" s="4"/>
+      <c r="BW17" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX17" s="4"/>
       <c r="BY17" s="4"/>
       <c r="BZ17" s="4"/>
@@ -5187,7 +5207,7 @@
       <c r="DR17" s="4"/>
       <c r="DS17" s="4"/>
     </row>
-    <row r="18" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132193</v>
       </c>
@@ -5410,7 +5430,9 @@
       <c r="BV18" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW18" s="4"/>
+      <c r="BW18" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX18" s="4"/>
       <c r="BY18" s="4"/>
       <c r="BZ18" s="4"/>
@@ -5460,7 +5482,7 @@
       <c r="DR18" s="4"/>
       <c r="DS18" s="4"/>
     </row>
-    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:123" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132263</v>
       </c>
@@ -5701,7 +5723,7 @@
       <c r="DR19" s="4"/>
       <c r="DS19" s="4"/>
     </row>
-    <row r="20" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132178</v>
       </c>
@@ -5924,7 +5946,9 @@
       <c r="BV20" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW20" s="4"/>
+      <c r="BW20" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX20" s="4"/>
       <c r="BY20" s="4"/>
       <c r="BZ20" s="4"/>
@@ -5974,7 +5998,7 @@
       <c r="DR20" s="4"/>
       <c r="DS20" s="4"/>
     </row>
-    <row r="21" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132222</v>
       </c>
@@ -6197,7 +6221,9 @@
       <c r="BV21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW21" s="4"/>
+      <c r="BW21" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX21" s="4"/>
       <c r="BY21" s="4"/>
       <c r="BZ21" s="4"/>
@@ -6247,7 +6273,7 @@
       <c r="DR21" s="4"/>
       <c r="DS21" s="4"/>
     </row>
-    <row r="22" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132224</v>
       </c>
@@ -6470,7 +6496,9 @@
       <c r="BV22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW22" s="4"/>
+      <c r="BW22" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX22" s="4"/>
       <c r="BY22" s="4"/>
       <c r="BZ22" s="4"/>
@@ -6520,7 +6548,7 @@
       <c r="DR22" s="4"/>
       <c r="DS22" s="4"/>
     </row>
-    <row r="23" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26132226</v>
       </c>
@@ -6743,7 +6771,9 @@
       <c r="BV23" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW23" s="4"/>
+      <c r="BW23" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX23" s="4"/>
       <c r="BY23" s="4"/>
       <c r="BZ23" s="4"/>
@@ -6793,7 +6823,7 @@
       <c r="DR23" s="4"/>
       <c r="DS23" s="4"/>
     </row>
-    <row r="24" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26133031</v>
       </c>
@@ -6995,7 +7025,9 @@
       <c r="BV24" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW24" s="4"/>
+      <c r="BW24" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX24" s="4"/>
       <c r="BY24" s="4"/>
       <c r="BZ24" s="4"/>
@@ -7045,7 +7077,7 @@
       <c r="DR24" s="4"/>
       <c r="DS24" s="4"/>
     </row>
-    <row r="25" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132228</v>
       </c>
@@ -7268,7 +7300,9 @@
       <c r="BV25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW25" s="4"/>
+      <c r="BW25" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX25" s="4"/>
       <c r="BY25" s="4"/>
       <c r="BZ25" s="4"/>
@@ -7318,7 +7352,7 @@
       <c r="DR25" s="4"/>
       <c r="DS25" s="4"/>
     </row>
-    <row r="26" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132284</v>
       </c>
@@ -7541,7 +7575,9 @@
       <c r="BV26" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW26" s="4"/>
+      <c r="BW26" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX26" s="4"/>
       <c r="BY26" s="4"/>
       <c r="BZ26" s="4"/>
@@ -7591,7 +7627,7 @@
       <c r="DR26" s="4"/>
       <c r="DS26" s="4"/>
     </row>
-    <row r="27" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132267</v>
       </c>
@@ -7814,7 +7850,9 @@
       <c r="BV27" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW27" s="4"/>
+      <c r="BW27" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX27" s="4"/>
       <c r="BY27" s="4"/>
       <c r="BZ27" s="4"/>
@@ -7864,7 +7902,7 @@
       <c r="DR27" s="4"/>
       <c r="DS27" s="4"/>
     </row>
-    <row r="28" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132279</v>
       </c>
@@ -8087,7 +8125,9 @@
       <c r="BV28" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW28" s="4"/>
+      <c r="BW28" s="4" t="s">
+        <v>6</v>
+      </c>
       <c r="BX28" s="4"/>
       <c r="BY28" s="4"/>
       <c r="BZ28" s="4"/>
@@ -8137,7 +8177,7 @@
       <c r="DR28" s="4"/>
       <c r="DS28" s="4"/>
     </row>
-    <row r="29" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132230</v>
       </c>
@@ -8360,7 +8400,9 @@
       <c r="BV29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW29" s="4"/>
+      <c r="BW29" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX29" s="4"/>
       <c r="BY29" s="4"/>
       <c r="BZ29" s="4"/>
@@ -8410,7 +8452,7 @@
       <c r="DR29" s="4"/>
       <c r="DS29" s="4"/>
     </row>
-    <row r="30" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132191</v>
       </c>
@@ -8633,7 +8675,9 @@
       <c r="BV30" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW30" s="4"/>
+      <c r="BW30" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX30" s="4"/>
       <c r="BY30" s="4"/>
       <c r="BZ30" s="4"/>
@@ -8683,7 +8727,7 @@
       <c r="DR30" s="4"/>
       <c r="DS30" s="4"/>
     </row>
-    <row r="31" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132182</v>
       </c>
@@ -8906,7 +8950,9 @@
       <c r="BV31" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="BW31" s="4"/>
+      <c r="BW31" s="4" t="s">
+        <v>5</v>
+      </c>
       <c r="BX31" s="4"/>
       <c r="BY31" s="4"/>
       <c r="BZ31" s="4"/>
@@ -8956,7 +9002,7 @@
       <c r="DR31" s="4"/>
       <c r="DS31" s="4"/>
     </row>
-    <row r="32" spans="1:123" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:123" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132236</v>
       </c>
@@ -9179,8 +9225,11 @@
       <c r="BV32" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="BW32" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="33" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132188</v>
       </c>
@@ -9403,8 +9452,11 @@
       <c r="BV33" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="BW33" s="4" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="34" spans="1:74" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:75" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>26132234</v>
       </c>
@@ -9625,6 +9677,9 @@
         <v>7</v>
       </c>
       <c r="BV34" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="BW34" s="4" t="s">
         <v>5</v>
       </c>
     </row>
@@ -9633,7 +9688,7 @@
     <sortCondition ref="B3:B34"/>
   </sortState>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D3:N3 BI3:BT3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:BG31 BV3:DG31 O3:AT34 BI4:BO4 D4:I31 K4:M31 J4:J34 N4:N34 BP4:BT34 AZ5:AZ10 BL5:BO12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:BO31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34 BO32:BO34 BV32:BV34">
+  <conditionalFormatting sqref="D3:N3 BI3:BT3 AV3:AZ4 BB3:BB22 BC3:BC31 BF3:BG31 BV3:DG31 O3:AT34 BI4:BO4 D4:I31 K4:M31 J4:J34 N4:N34 BP4:BT34 AZ5:AZ10 BL5:BO12 AV5:AX31 BI5:BJ31 AY5:AY34 BK5:BK34 AZ11:BA22 BD11:BE31 BM13:BO31 BL13:BL34 AZ23:BB31 G32:I32 AV32:AV34 BO32:BO34 BV32:BW34">
     <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -9671,13 +9726,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAA43B27-548D-428E-B1BF-5E790279A96A}">
   <dimension ref="A1:B33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -9685,7 +9740,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>26132174</v>
       </c>
@@ -9693,7 +9748,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>26132207</v>
       </c>
@@ -9701,7 +9756,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>26132186</v>
       </c>
@@ -9709,7 +9764,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>26132259</v>
       </c>
@@ -9717,7 +9772,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>26133017</v>
       </c>
@@ -9725,7 +9780,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>26132209</v>
       </c>
@@ -9733,7 +9788,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>26132211</v>
       </c>
@@ -9741,7 +9796,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>26132215</v>
       </c>
@@ -9749,7 +9804,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>26132213</v>
       </c>
@@ -9757,7 +9812,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>26132261</v>
       </c>
@@ -9765,7 +9820,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>26133027</v>
       </c>
@@ -9773,7 +9828,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>26132176</v>
       </c>
@@ -9781,7 +9836,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>26132254</v>
       </c>
@@ -9789,7 +9844,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>26132326</v>
       </c>
@@ -9797,7 +9852,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>26132195</v>
       </c>
@@ -9805,7 +9860,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>26132193</v>
       </c>
@@ -9813,7 +9868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>26132263</v>
       </c>
@@ -9821,7 +9876,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>26132178</v>
       </c>
@@ -9829,7 +9884,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>26132222</v>
       </c>
@@ -9837,7 +9892,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>26132224</v>
       </c>
@@ -9845,7 +9900,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>26132226</v>
       </c>
@@ -9853,7 +9908,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>26133031</v>
       </c>
@@ -9861,7 +9916,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>26132228</v>
       </c>
@@ -9869,7 +9924,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26132284</v>
       </c>
@@ -9877,7 +9932,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>26132267</v>
       </c>
@@ -9885,7 +9940,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>26132279</v>
       </c>
@@ -9893,7 +9948,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>26132230</v>
       </c>
@@ -9901,7 +9956,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>26132191</v>
       </c>
@@ -9909,7 +9964,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>26132182</v>
       </c>
@@ -9917,7 +9972,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>26132236</v>
       </c>
@@ -9925,7 +9980,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>26132188</v>
       </c>
@@ -9933,7 +9988,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>26132234</v>
       </c>
